--- a/data/kriter_veri_seti_2022.xlsx
+++ b/data/kriter_veri_seti_2022.xlsx
@@ -413,41 +413,61 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G73"/>
+  <dimension ref="A1:K73"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="inlineStr">
         <is>
+          <t>fakulte</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>bolum</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>yil</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t>donem</t>
+        </is>
+      </c>
+      <c r="E1" t="inlineStr">
+        <is>
           <t>ders_kodu</t>
         </is>
       </c>
-      <c r="B1" t="inlineStr">
-        <is>
-          <t>donem</t>
-        </is>
-      </c>
-      <c r="C1" t="inlineStr">
+      <c r="F1" t="inlineStr">
+        <is>
+          <t>ders_adi</t>
+        </is>
+      </c>
+      <c r="G1" t="inlineStr">
         <is>
           <t>toplam_ogrenci</t>
         </is>
       </c>
-      <c r="D1" t="inlineStr">
+      <c r="H1" t="inlineStr">
         <is>
           <t>gecen_ogrenci</t>
         </is>
       </c>
-      <c r="E1" t="inlineStr">
+      <c r="I1" t="inlineStr">
         <is>
           <t>basari_ortalamasi</t>
         </is>
       </c>
-      <c r="F1" t="inlineStr">
+      <c r="J1" t="inlineStr">
         <is>
           <t>kontenjan</t>
         </is>
       </c>
-      <c r="G1" t="inlineStr">
+      <c r="K1" t="inlineStr">
         <is>
           <t>kayitli_ogrenci</t>
         </is>
@@ -456,1944 +476,3240 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
+          <t>Tıp Fakültesi</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>Tıp</t>
+        </is>
+      </c>
+      <c r="C2" t="n">
+        <v>2022</v>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>Bahar</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
           <t>OZD062</t>
         </is>
       </c>
-      <c r="B2" t="inlineStr">
-        <is>
-          <t>Bahar</t>
-        </is>
-      </c>
-      <c r="C2" t="n">
-        <v>50</v>
-      </c>
-      <c r="D2" t="n">
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>Iletisim Becerileri</t>
+        </is>
+      </c>
+      <c r="G2" t="n">
+        <v>50</v>
+      </c>
+      <c r="H2" t="n">
         <v>45</v>
       </c>
-      <c r="E2" t="n">
+      <c r="I2" t="n">
         <v>80.5</v>
       </c>
-      <c r="F2" t="n">
-        <v>60</v>
-      </c>
-      <c r="G2" t="n">
+      <c r="J2" t="n">
+        <v>60</v>
+      </c>
+      <c r="K2" t="n">
         <v>50</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
+          <t>Tıp Fakültesi</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>Tıp</t>
+        </is>
+      </c>
+      <c r="C3" t="n">
+        <v>2022</v>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>Bahar</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
           <t>OZD064</t>
         </is>
       </c>
-      <c r="B3" t="inlineStr">
-        <is>
-          <t>Bahar</t>
-        </is>
-      </c>
-      <c r="C3" t="n">
-        <v>50</v>
-      </c>
-      <c r="D3" t="n">
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>Arastirma Yontemleri</t>
+        </is>
+      </c>
+      <c r="G3" t="n">
+        <v>50</v>
+      </c>
+      <c r="H3" t="n">
         <v>46</v>
       </c>
-      <c r="E3" t="n">
+      <c r="I3" t="n">
         <v>81.63</v>
       </c>
-      <c r="F3" t="n">
-        <v>60</v>
-      </c>
-      <c r="G3" t="n">
+      <c r="J3" t="n">
+        <v>60</v>
+      </c>
+      <c r="K3" t="n">
         <v>50</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
+          <t>Tıp Fakültesi</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>Tıp</t>
+        </is>
+      </c>
+      <c r="C4" t="n">
+        <v>2022</v>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>Bahar</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
           <t>TIP609</t>
         </is>
       </c>
-      <c r="B4" t="inlineStr">
-        <is>
-          <t>Bahar</t>
-        </is>
-      </c>
-      <c r="C4" t="n">
-        <v>50</v>
-      </c>
-      <c r="D4" t="n">
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Klinik Farmakoloji</t>
+        </is>
+      </c>
+      <c r="G4" t="n">
+        <v>50</v>
+      </c>
+      <c r="H4" t="n">
         <v>43</v>
       </c>
-      <c r="E4" t="n">
+      <c r="I4" t="n">
         <v>79.81</v>
       </c>
-      <c r="F4" t="n">
-        <v>60</v>
-      </c>
-      <c r="G4" t="n">
+      <c r="J4" t="n">
+        <v>60</v>
+      </c>
+      <c r="K4" t="n">
         <v>50</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
+          <t>Tıp Fakültesi</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>Tıp</t>
+        </is>
+      </c>
+      <c r="C5" t="n">
+        <v>2022</v>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>Bahar</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
           <t>TIP610</t>
         </is>
       </c>
-      <c r="B5" t="inlineStr">
-        <is>
-          <t>Bahar</t>
-        </is>
-      </c>
-      <c r="C5" t="n">
-        <v>50</v>
-      </c>
-      <c r="D5" t="n">
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Ileri Fizyoloji</t>
+        </is>
+      </c>
+      <c r="G5" t="n">
+        <v>50</v>
+      </c>
+      <c r="H5" t="n">
         <v>46</v>
       </c>
-      <c r="E5" t="n">
+      <c r="I5" t="n">
         <v>80.84</v>
       </c>
-      <c r="F5" t="n">
-        <v>60</v>
-      </c>
-      <c r="G5" t="n">
+      <c r="J5" t="n">
+        <v>60</v>
+      </c>
+      <c r="K5" t="n">
         <v>50</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
+          <t>Tıp Fakültesi</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>Tıp</t>
+        </is>
+      </c>
+      <c r="C6" t="n">
+        <v>2022</v>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>Guz</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
           <t>OZD061</t>
         </is>
       </c>
-      <c r="B6" t="inlineStr">
-        <is>
-          <t>Guz</t>
-        </is>
-      </c>
-      <c r="C6" t="n">
-        <v>50</v>
-      </c>
-      <c r="D6" t="n">
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Girisimcilik</t>
+        </is>
+      </c>
+      <c r="G6" t="n">
+        <v>50</v>
+      </c>
+      <c r="H6" t="n">
         <v>42</v>
       </c>
-      <c r="E6" t="n">
+      <c r="I6" t="n">
         <v>79.31</v>
       </c>
-      <c r="F6" t="n">
-        <v>60</v>
-      </c>
-      <c r="G6" t="n">
+      <c r="J6" t="n">
+        <v>60</v>
+      </c>
+      <c r="K6" t="n">
         <v>50</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
+          <t>Tıp Fakültesi</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>Tıp</t>
+        </is>
+      </c>
+      <c r="C7" t="n">
+        <v>2022</v>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>Guz</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
           <t>OZD063</t>
         </is>
       </c>
-      <c r="B7" t="inlineStr">
-        <is>
-          <t>Guz</t>
-        </is>
-      </c>
-      <c r="C7" t="n">
-        <v>50</v>
-      </c>
-      <c r="D7" t="n">
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>Toplum Projesi</t>
+        </is>
+      </c>
+      <c r="G7" t="n">
+        <v>50</v>
+      </c>
+      <c r="H7" t="n">
         <v>47</v>
       </c>
-      <c r="E7" t="n">
+      <c r="I7" t="n">
         <v>82.73</v>
       </c>
-      <c r="F7" t="n">
-        <v>60</v>
-      </c>
-      <c r="G7" t="n">
+      <c r="J7" t="n">
+        <v>60</v>
+      </c>
+      <c r="K7" t="n">
         <v>50</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
+          <t>Tıp Fakültesi</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>Tıp</t>
+        </is>
+      </c>
+      <c r="C8" t="n">
+        <v>2022</v>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>Guz</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
           <t>TIP101S</t>
         </is>
       </c>
-      <c r="B8" t="inlineStr">
-        <is>
-          <t>Guz</t>
-        </is>
-      </c>
-      <c r="C8" t="n">
-        <v>50</v>
-      </c>
-      <c r="D8" t="n">
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>Klinik Anatomi Secmeli</t>
+        </is>
+      </c>
+      <c r="G8" t="n">
+        <v>50</v>
+      </c>
+      <c r="H8" t="n">
         <v>44</v>
       </c>
-      <c r="E8" t="n">
+      <c r="I8" t="n">
         <v>80.97</v>
       </c>
-      <c r="F8" t="n">
-        <v>60</v>
-      </c>
-      <c r="G8" t="n">
+      <c r="J8" t="n">
+        <v>60</v>
+      </c>
+      <c r="K8" t="n">
         <v>50</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
+          <t>Tıp Fakültesi</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>Tıp</t>
+        </is>
+      </c>
+      <c r="C9" t="n">
+        <v>2022</v>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>Guz</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
           <t>TIP102S</t>
         </is>
       </c>
-      <c r="B9" t="inlineStr">
-        <is>
-          <t>Guz</t>
-        </is>
-      </c>
-      <c r="C9" t="n">
-        <v>50</v>
-      </c>
-      <c r="D9" t="n">
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>Tibbi Etik Secmeli</t>
+        </is>
+      </c>
+      <c r="G9" t="n">
+        <v>50</v>
+      </c>
+      <c r="H9" t="n">
         <v>48</v>
       </c>
-      <c r="E9" t="n">
+      <c r="I9" t="n">
         <v>82.25</v>
       </c>
-      <c r="F9" t="n">
-        <v>60</v>
-      </c>
-      <c r="G9" t="n">
+      <c r="J9" t="n">
+        <v>60</v>
+      </c>
+      <c r="K9" t="n">
         <v>50</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
+          <t>Mühendislik ve Doğa Bilimleri Fakültesi</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>Bilgisayar Mühendisliği</t>
+        </is>
+      </c>
+      <c r="C10" t="n">
+        <v>2022</v>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>Bahar</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
           <t>BMB402S</t>
         </is>
       </c>
-      <c r="B10" t="inlineStr">
-        <is>
-          <t>Bahar</t>
-        </is>
-      </c>
-      <c r="C10" t="n">
-        <v>50</v>
-      </c>
-      <c r="D10" t="n">
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>Derin Ogrenme</t>
+        </is>
+      </c>
+      <c r="G10" t="n">
+        <v>50</v>
+      </c>
+      <c r="H10" t="n">
         <v>43</v>
       </c>
-      <c r="E10" t="n">
+      <c r="I10" t="n">
         <v>77.79000000000001</v>
       </c>
-      <c r="F10" t="n">
-        <v>60</v>
-      </c>
-      <c r="G10" t="n">
+      <c r="J10" t="n">
+        <v>60</v>
+      </c>
+      <c r="K10" t="n">
         <v>50</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
+          <t>Mühendislik ve Doğa Bilimleri Fakültesi</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>Bilgisayar Mühendisliği</t>
+        </is>
+      </c>
+      <c r="C11" t="n">
+        <v>2022</v>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>Bahar</t>
+        </is>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
           <t>BMB404S</t>
         </is>
       </c>
-      <c r="B11" t="inlineStr">
-        <is>
-          <t>Bahar</t>
-        </is>
-      </c>
-      <c r="C11" t="n">
-        <v>50</v>
-      </c>
-      <c r="D11" t="n">
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>Buyuk Veri Analizi</t>
+        </is>
+      </c>
+      <c r="G11" t="n">
+        <v>50</v>
+      </c>
+      <c r="H11" t="n">
         <v>42</v>
       </c>
-      <c r="E11" t="n">
+      <c r="I11" t="n">
         <v>78.16</v>
       </c>
-      <c r="F11" t="n">
-        <v>60</v>
-      </c>
-      <c r="G11" t="n">
+      <c r="J11" t="n">
+        <v>60</v>
+      </c>
+      <c r="K11" t="n">
         <v>50</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
+          <t>Mühendislik ve Doğa Bilimleri Fakültesi</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>Bilgisayar Mühendisliği</t>
+        </is>
+      </c>
+      <c r="C12" t="n">
+        <v>2022</v>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>Bahar</t>
+        </is>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
           <t>BMB406S</t>
         </is>
       </c>
-      <c r="B12" t="inlineStr">
-        <is>
-          <t>Bahar</t>
-        </is>
-      </c>
-      <c r="C12" t="n">
-        <v>50</v>
-      </c>
-      <c r="D12" t="n">
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>Oyun Gelistirme</t>
+        </is>
+      </c>
+      <c r="G12" t="n">
+        <v>50</v>
+      </c>
+      <c r="H12" t="n">
         <v>40</v>
       </c>
-      <c r="E12" t="n">
+      <c r="I12" t="n">
         <v>74.89</v>
       </c>
-      <c r="F12" t="n">
-        <v>60</v>
-      </c>
-      <c r="G12" t="n">
+      <c r="J12" t="n">
+        <v>60</v>
+      </c>
+      <c r="K12" t="n">
         <v>50</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
+          <t>Mühendislik ve Doğa Bilimleri Fakültesi</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>Bilgisayar Mühendisliği</t>
+        </is>
+      </c>
+      <c r="C13" t="n">
+        <v>2022</v>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>Bahar</t>
+        </is>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
           <t>BMB408S</t>
         </is>
       </c>
-      <c r="B13" t="inlineStr">
-        <is>
-          <t>Bahar</t>
-        </is>
-      </c>
-      <c r="C13" t="n">
-        <v>50</v>
-      </c>
-      <c r="D13" t="n">
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>Dogal Dil Isleme</t>
+        </is>
+      </c>
+      <c r="G13" t="n">
+        <v>50</v>
+      </c>
+      <c r="H13" t="n">
         <v>39</v>
       </c>
-      <c r="E13" t="n">
+      <c r="I13" t="n">
         <v>75.59999999999999</v>
       </c>
-      <c r="F13" t="n">
-        <v>60</v>
-      </c>
-      <c r="G13" t="n">
+      <c r="J13" t="n">
+        <v>60</v>
+      </c>
+      <c r="K13" t="n">
         <v>50</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
+          <t>Mühendislik ve Doğa Bilimleri Fakültesi</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>Bilgisayar Mühendisliği</t>
+        </is>
+      </c>
+      <c r="C14" t="n">
+        <v>2022</v>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>Guz</t>
+        </is>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
           <t>BMB401S</t>
         </is>
       </c>
-      <c r="B14" t="inlineStr">
-        <is>
-          <t>Guz</t>
-        </is>
-      </c>
-      <c r="C14" t="n">
-        <v>50</v>
-      </c>
-      <c r="D14" t="n">
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>Makine Ogrenmesi</t>
+        </is>
+      </c>
+      <c r="G14" t="n">
+        <v>50</v>
+      </c>
+      <c r="H14" t="n">
         <v>41</v>
       </c>
-      <c r="E14" t="n">
+      <c r="I14" t="n">
         <v>77.95999999999999</v>
       </c>
-      <c r="F14" t="n">
-        <v>60</v>
-      </c>
-      <c r="G14" t="n">
+      <c r="J14" t="n">
+        <v>60</v>
+      </c>
+      <c r="K14" t="n">
         <v>50</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
+          <t>Mühendislik ve Doğa Bilimleri Fakültesi</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>Bilgisayar Mühendisliği</t>
+        </is>
+      </c>
+      <c r="C15" t="n">
+        <v>2022</v>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>Guz</t>
+        </is>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
           <t>BMB403S</t>
         </is>
       </c>
-      <c r="B15" t="inlineStr">
-        <is>
-          <t>Guz</t>
-        </is>
-      </c>
-      <c r="C15" t="n">
-        <v>50</v>
-      </c>
-      <c r="D15" t="n">
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>Bulut Bilisim</t>
+        </is>
+      </c>
+      <c r="G15" t="n">
+        <v>50</v>
+      </c>
+      <c r="H15" t="n">
         <v>43</v>
       </c>
-      <c r="E15" t="n">
+      <c r="I15" t="n">
         <v>76.7</v>
       </c>
-      <c r="F15" t="n">
-        <v>60</v>
-      </c>
-      <c r="G15" t="n">
+      <c r="J15" t="n">
+        <v>60</v>
+      </c>
+      <c r="K15" t="n">
         <v>50</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
+          <t>Mühendislik ve Doğa Bilimleri Fakültesi</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>Bilgisayar Mühendisliği</t>
+        </is>
+      </c>
+      <c r="C16" t="n">
+        <v>2022</v>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>Guz</t>
+        </is>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
           <t>BMB405S</t>
         </is>
       </c>
-      <c r="B16" t="inlineStr">
-        <is>
-          <t>Guz</t>
-        </is>
-      </c>
-      <c r="C16" t="n">
-        <v>50</v>
-      </c>
-      <c r="D16" t="n">
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>Mobil Uygulama Gelistirme</t>
+        </is>
+      </c>
+      <c r="G16" t="n">
+        <v>50</v>
+      </c>
+      <c r="H16" t="n">
         <v>44</v>
       </c>
-      <c r="E16" t="n">
+      <c r="I16" t="n">
         <v>76.42</v>
       </c>
-      <c r="F16" t="n">
-        <v>60</v>
-      </c>
-      <c r="G16" t="n">
+      <c r="J16" t="n">
+        <v>60</v>
+      </c>
+      <c r="K16" t="n">
         <v>50</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
+          <t>Mühendislik ve Doğa Bilimleri Fakültesi</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>Bilgisayar Mühendisliği</t>
+        </is>
+      </c>
+      <c r="C17" t="n">
+        <v>2022</v>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>Guz</t>
+        </is>
+      </c>
+      <c r="E17" t="inlineStr">
+        <is>
           <t>BMB407S</t>
         </is>
       </c>
-      <c r="B17" t="inlineStr">
-        <is>
-          <t>Guz</t>
-        </is>
-      </c>
-      <c r="C17" t="n">
-        <v>50</v>
-      </c>
-      <c r="D17" t="n">
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>Siber Guvenlik</t>
+        </is>
+      </c>
+      <c r="G17" t="n">
+        <v>50</v>
+      </c>
+      <c r="H17" t="n">
         <v>44</v>
       </c>
-      <c r="E17" t="n">
+      <c r="I17" t="n">
         <v>77.5</v>
       </c>
-      <c r="F17" t="n">
-        <v>60</v>
-      </c>
-      <c r="G17" t="n">
+      <c r="J17" t="n">
+        <v>60</v>
+      </c>
+      <c r="K17" t="n">
         <v>50</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
+          <t>Mühendislik ve Doğa Bilimleri Fakültesi</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>Elektrik-Elektronik Mühendisliği</t>
+        </is>
+      </c>
+      <c r="C18" t="n">
+        <v>2022</v>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>Bahar</t>
+        </is>
+      </c>
+      <c r="E18" t="inlineStr">
+        <is>
           <t>EEM402S</t>
         </is>
       </c>
-      <c r="B18" t="inlineStr">
-        <is>
-          <t>Bahar</t>
-        </is>
-      </c>
-      <c r="C18" t="n">
-        <v>50</v>
-      </c>
-      <c r="D18" t="n">
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>Nesnelerin Interneti</t>
+        </is>
+      </c>
+      <c r="G18" t="n">
+        <v>50</v>
+      </c>
+      <c r="H18" t="n">
         <v>44</v>
       </c>
-      <c r="E18" t="n">
+      <c r="I18" t="n">
         <v>77.34</v>
       </c>
-      <c r="F18" t="n">
-        <v>60</v>
-      </c>
-      <c r="G18" t="n">
+      <c r="J18" t="n">
+        <v>60</v>
+      </c>
+      <c r="K18" t="n">
         <v>50</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
+          <t>Mühendislik ve Doğa Bilimleri Fakültesi</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>Elektrik-Elektronik Mühendisliği</t>
+        </is>
+      </c>
+      <c r="C19" t="n">
+        <v>2022</v>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>Bahar</t>
+        </is>
+      </c>
+      <c r="E19" t="inlineStr">
+        <is>
           <t>EEM404S</t>
         </is>
       </c>
-      <c r="B19" t="inlineStr">
-        <is>
-          <t>Bahar</t>
-        </is>
-      </c>
-      <c r="C19" t="n">
-        <v>50</v>
-      </c>
-      <c r="D19" t="n">
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>Yenilenebilir Enerji</t>
+        </is>
+      </c>
+      <c r="G19" t="n">
+        <v>50</v>
+      </c>
+      <c r="H19" t="n">
         <v>43</v>
       </c>
-      <c r="E19" t="n">
+      <c r="I19" t="n">
         <v>77.58</v>
       </c>
-      <c r="F19" t="n">
-        <v>60</v>
-      </c>
-      <c r="G19" t="n">
+      <c r="J19" t="n">
+        <v>60</v>
+      </c>
+      <c r="K19" t="n">
         <v>50</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
+          <t>Mühendislik ve Doğa Bilimleri Fakültesi</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>Elektrik-Elektronik Mühendisliği</t>
+        </is>
+      </c>
+      <c r="C20" t="n">
+        <v>2022</v>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>Bahar</t>
+        </is>
+      </c>
+      <c r="E20" t="inlineStr">
+        <is>
           <t>EEM406S</t>
         </is>
       </c>
-      <c r="B20" t="inlineStr">
-        <is>
-          <t>Bahar</t>
-        </is>
-      </c>
-      <c r="C20" t="n">
-        <v>50</v>
-      </c>
-      <c r="D20" t="n">
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>Robot Kontrolu</t>
+        </is>
+      </c>
+      <c r="G20" t="n">
+        <v>50</v>
+      </c>
+      <c r="H20" t="n">
         <v>42</v>
       </c>
-      <c r="E20" t="n">
+      <c r="I20" t="n">
         <v>78.17</v>
       </c>
-      <c r="F20" t="n">
-        <v>60</v>
-      </c>
-      <c r="G20" t="n">
+      <c r="J20" t="n">
+        <v>60</v>
+      </c>
+      <c r="K20" t="n">
         <v>50</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
+          <t>Mühendislik ve Doğa Bilimleri Fakültesi</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>Elektrik-Elektronik Mühendisliği</t>
+        </is>
+      </c>
+      <c r="C21" t="n">
+        <v>2022</v>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>Bahar</t>
+        </is>
+      </c>
+      <c r="E21" t="inlineStr">
+        <is>
           <t>EEM408S</t>
         </is>
       </c>
-      <c r="B21" t="inlineStr">
-        <is>
-          <t>Bahar</t>
-        </is>
-      </c>
-      <c r="C21" t="n">
-        <v>50</v>
-      </c>
-      <c r="D21" t="n">
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>Sinyal Isleme</t>
+        </is>
+      </c>
+      <c r="G21" t="n">
+        <v>50</v>
+      </c>
+      <c r="H21" t="n">
         <v>46</v>
       </c>
-      <c r="E21" t="n">
+      <c r="I21" t="n">
         <v>78.95999999999999</v>
       </c>
-      <c r="F21" t="n">
-        <v>60</v>
-      </c>
-      <c r="G21" t="n">
+      <c r="J21" t="n">
+        <v>60</v>
+      </c>
+      <c r="K21" t="n">
         <v>50</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
+          <t>Mühendislik ve Doğa Bilimleri Fakültesi</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>Elektrik-Elektronik Mühendisliği</t>
+        </is>
+      </c>
+      <c r="C22" t="n">
+        <v>2022</v>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>Guz</t>
+        </is>
+      </c>
+      <c r="E22" t="inlineStr">
+        <is>
           <t>EEM401S</t>
         </is>
       </c>
-      <c r="B22" t="inlineStr">
-        <is>
-          <t>Guz</t>
-        </is>
-      </c>
-      <c r="C22" t="n">
-        <v>50</v>
-      </c>
-      <c r="D22" t="n">
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>Kablosuz Haberlesme</t>
+        </is>
+      </c>
+      <c r="G22" t="n">
+        <v>50</v>
+      </c>
+      <c r="H22" t="n">
         <v>44</v>
       </c>
-      <c r="E22" t="n">
+      <c r="I22" t="n">
         <v>78.22</v>
       </c>
-      <c r="F22" t="n">
-        <v>60</v>
-      </c>
-      <c r="G22" t="n">
+      <c r="J22" t="n">
+        <v>60</v>
+      </c>
+      <c r="K22" t="n">
         <v>50</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
+          <t>Mühendislik ve Doğa Bilimleri Fakültesi</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>Elektrik-Elektronik Mühendisliği</t>
+        </is>
+      </c>
+      <c r="C23" t="n">
+        <v>2022</v>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>Guz</t>
+        </is>
+      </c>
+      <c r="E23" t="inlineStr">
+        <is>
           <t>EEM403S</t>
         </is>
       </c>
-      <c r="B23" t="inlineStr">
-        <is>
-          <t>Guz</t>
-        </is>
-      </c>
-      <c r="C23" t="n">
-        <v>50</v>
-      </c>
-      <c r="D23" t="n">
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>Guc Elektroniği</t>
+        </is>
+      </c>
+      <c r="G23" t="n">
+        <v>50</v>
+      </c>
+      <c r="H23" t="n">
         <v>47</v>
       </c>
-      <c r="E23" t="n">
+      <c r="I23" t="n">
         <v>79.40000000000001</v>
       </c>
-      <c r="F23" t="n">
-        <v>60</v>
-      </c>
-      <c r="G23" t="n">
+      <c r="J23" t="n">
+        <v>60</v>
+      </c>
+      <c r="K23" t="n">
         <v>50</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
+          <t>Mühendislik ve Doğa Bilimleri Fakültesi</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>Elektrik-Elektronik Mühendisliği</t>
+        </is>
+      </c>
+      <c r="C24" t="n">
+        <v>2022</v>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>Guz</t>
+        </is>
+      </c>
+      <c r="E24" t="inlineStr">
+        <is>
           <t>EEM405S</t>
         </is>
       </c>
-      <c r="B24" t="inlineStr">
-        <is>
-          <t>Guz</t>
-        </is>
-      </c>
-      <c r="C24" t="n">
-        <v>50</v>
-      </c>
-      <c r="D24" t="n">
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>Goruntu Isleme</t>
+        </is>
+      </c>
+      <c r="G24" t="n">
+        <v>50</v>
+      </c>
+      <c r="H24" t="n">
         <v>44</v>
       </c>
-      <c r="E24" t="n">
+      <c r="I24" t="n">
         <v>80.65000000000001</v>
       </c>
-      <c r="F24" t="n">
-        <v>60</v>
-      </c>
-      <c r="G24" t="n">
+      <c r="J24" t="n">
+        <v>60</v>
+      </c>
+      <c r="K24" t="n">
         <v>50</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
+          <t>Mühendislik ve Doğa Bilimleri Fakültesi</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>Elektrik-Elektronik Mühendisliği</t>
+        </is>
+      </c>
+      <c r="C25" t="n">
+        <v>2022</v>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>Guz</t>
+        </is>
+      </c>
+      <c r="E25" t="inlineStr">
+        <is>
           <t>EEM407S</t>
         </is>
       </c>
-      <c r="B25" t="inlineStr">
-        <is>
-          <t>Guz</t>
-        </is>
-      </c>
-      <c r="C25" t="n">
-        <v>50</v>
-      </c>
-      <c r="D25" t="n">
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>Gomulu Sistemler</t>
+        </is>
+      </c>
+      <c r="G25" t="n">
+        <v>50</v>
+      </c>
+      <c r="H25" t="n">
         <v>45</v>
       </c>
-      <c r="E25" t="n">
+      <c r="I25" t="n">
         <v>78.67</v>
       </c>
-      <c r="F25" t="n">
-        <v>60</v>
-      </c>
-      <c r="G25" t="n">
+      <c r="J25" t="n">
+        <v>60</v>
+      </c>
+      <c r="K25" t="n">
         <v>50</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
+          <t>Mühendislik ve Doğa Bilimleri Fakültesi</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>Endüstri Mühendisliği</t>
+        </is>
+      </c>
+      <c r="C26" t="n">
+        <v>2022</v>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>Bahar</t>
+        </is>
+      </c>
+      <c r="E26" t="inlineStr">
+        <is>
           <t>END402S</t>
         </is>
       </c>
-      <c r="B26" t="inlineStr">
-        <is>
-          <t>Bahar</t>
-        </is>
-      </c>
-      <c r="C26" t="n">
-        <v>50</v>
-      </c>
-      <c r="D26" t="n">
+      <c r="F26" t="inlineStr">
+        <is>
+          <t>Yapay Zeka Uygulamalari</t>
+        </is>
+      </c>
+      <c r="G26" t="n">
+        <v>50</v>
+      </c>
+      <c r="H26" t="n">
         <v>40</v>
       </c>
-      <c r="E26" t="n">
+      <c r="I26" t="n">
         <v>74.59999999999999</v>
       </c>
-      <c r="F26" t="n">
-        <v>60</v>
-      </c>
-      <c r="G26" t="n">
+      <c r="J26" t="n">
+        <v>60</v>
+      </c>
+      <c r="K26" t="n">
         <v>50</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
+          <t>Mühendislik ve Doğa Bilimleri Fakültesi</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>Endüstri Mühendisliği</t>
+        </is>
+      </c>
+      <c r="C27" t="n">
+        <v>2022</v>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>Bahar</t>
+        </is>
+      </c>
+      <c r="E27" t="inlineStr">
+        <is>
           <t>END404S</t>
         </is>
       </c>
-      <c r="B27" t="inlineStr">
-        <is>
-          <t>Bahar</t>
-        </is>
-      </c>
-      <c r="C27" t="n">
-        <v>50</v>
-      </c>
-      <c r="D27" t="n">
+      <c r="F27" t="inlineStr">
+        <is>
+          <t>Veri Madenciligi</t>
+        </is>
+      </c>
+      <c r="G27" t="n">
+        <v>50</v>
+      </c>
+      <c r="H27" t="n">
         <v>42</v>
       </c>
-      <c r="E27" t="n">
+      <c r="I27" t="n">
         <v>76.20999999999999</v>
       </c>
-      <c r="F27" t="n">
-        <v>60</v>
-      </c>
-      <c r="G27" t="n">
+      <c r="J27" t="n">
+        <v>60</v>
+      </c>
+      <c r="K27" t="n">
         <v>50</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
+          <t>Mühendislik ve Doğa Bilimleri Fakültesi</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>Endüstri Mühendisliği</t>
+        </is>
+      </c>
+      <c r="C28" t="n">
+        <v>2022</v>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>Bahar</t>
+        </is>
+      </c>
+      <c r="E28" t="inlineStr">
+        <is>
           <t>END406S</t>
         </is>
       </c>
-      <c r="B28" t="inlineStr">
-        <is>
-          <t>Bahar</t>
-        </is>
-      </c>
-      <c r="C28" t="n">
-        <v>50</v>
-      </c>
-      <c r="D28" t="n">
+      <c r="F28" t="inlineStr">
+        <is>
+          <t>Ileri Uretim Sistemleri</t>
+        </is>
+      </c>
+      <c r="G28" t="n">
+        <v>50</v>
+      </c>
+      <c r="H28" t="n">
         <v>42</v>
       </c>
-      <c r="E28" t="n">
+      <c r="I28" t="n">
         <v>76.28</v>
       </c>
-      <c r="F28" t="n">
-        <v>60</v>
-      </c>
-      <c r="G28" t="n">
+      <c r="J28" t="n">
+        <v>60</v>
+      </c>
+      <c r="K28" t="n">
         <v>50</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
+          <t>Mühendislik ve Doğa Bilimleri Fakültesi</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>Endüstri Mühendisliği</t>
+        </is>
+      </c>
+      <c r="C29" t="n">
+        <v>2022</v>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>Bahar</t>
+        </is>
+      </c>
+      <c r="E29" t="inlineStr">
+        <is>
           <t>END408S</t>
         </is>
       </c>
-      <c r="B29" t="inlineStr">
-        <is>
-          <t>Bahar</t>
-        </is>
-      </c>
-      <c r="C29" t="n">
-        <v>50</v>
-      </c>
-      <c r="D29" t="n">
+      <c r="F29" t="inlineStr">
+        <is>
+          <t>Surec Simulasyonu</t>
+        </is>
+      </c>
+      <c r="G29" t="n">
+        <v>50</v>
+      </c>
+      <c r="H29" t="n">
         <v>43</v>
       </c>
-      <c r="E29" t="n">
+      <c r="I29" t="n">
         <v>79.06</v>
       </c>
-      <c r="F29" t="n">
-        <v>60</v>
-      </c>
-      <c r="G29" t="n">
+      <c r="J29" t="n">
+        <v>60</v>
+      </c>
+      <c r="K29" t="n">
         <v>50</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
+          <t>Mühendislik ve Doğa Bilimleri Fakültesi</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>Endüstri Mühendisliği</t>
+        </is>
+      </c>
+      <c r="C30" t="n">
+        <v>2022</v>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>Guz</t>
+        </is>
+      </c>
+      <c r="E30" t="inlineStr">
+        <is>
           <t>END401S</t>
         </is>
       </c>
-      <c r="B30" t="inlineStr">
-        <is>
-          <t>Guz</t>
-        </is>
-      </c>
-      <c r="C30" t="n">
-        <v>50</v>
-      </c>
-      <c r="D30" t="n">
+      <c r="F30" t="inlineStr">
+        <is>
+          <t>Tedarik Zinciri Yonetimi</t>
+        </is>
+      </c>
+      <c r="G30" t="n">
+        <v>50</v>
+      </c>
+      <c r="H30" t="n">
         <v>43</v>
       </c>
-      <c r="E30" t="n">
+      <c r="I30" t="n">
         <v>77.76000000000001</v>
       </c>
-      <c r="F30" t="n">
-        <v>60</v>
-      </c>
-      <c r="G30" t="n">
+      <c r="J30" t="n">
+        <v>60</v>
+      </c>
+      <c r="K30" t="n">
         <v>50</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
+          <t>Mühendislik ve Doğa Bilimleri Fakültesi</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>Endüstri Mühendisliği</t>
+        </is>
+      </c>
+      <c r="C31" t="n">
+        <v>2022</v>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>Guz</t>
+        </is>
+      </c>
+      <c r="E31" t="inlineStr">
+        <is>
           <t>END403S</t>
         </is>
       </c>
-      <c r="B31" t="inlineStr">
-        <is>
-          <t>Guz</t>
-        </is>
-      </c>
-      <c r="C31" t="n">
-        <v>50</v>
-      </c>
-      <c r="D31" t="n">
+      <c r="F31" t="inlineStr">
+        <is>
+          <t>Proje Yonetimi</t>
+        </is>
+      </c>
+      <c r="G31" t="n">
+        <v>50</v>
+      </c>
+      <c r="H31" t="n">
         <v>40</v>
       </c>
-      <c r="E31" t="n">
+      <c r="I31" t="n">
         <v>76.45999999999999</v>
       </c>
-      <c r="F31" t="n">
-        <v>60</v>
-      </c>
-      <c r="G31" t="n">
+      <c r="J31" t="n">
+        <v>60</v>
+      </c>
+      <c r="K31" t="n">
         <v>50</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
+          <t>Mühendislik ve Doğa Bilimleri Fakültesi</t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>Endüstri Mühendisliği</t>
+        </is>
+      </c>
+      <c r="C32" t="n">
+        <v>2022</v>
+      </c>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>Guz</t>
+        </is>
+      </c>
+      <c r="E32" t="inlineStr">
+        <is>
           <t>END405S</t>
         </is>
       </c>
-      <c r="B32" t="inlineStr">
-        <is>
-          <t>Guz</t>
-        </is>
-      </c>
-      <c r="C32" t="n">
-        <v>50</v>
-      </c>
-      <c r="D32" t="n">
+      <c r="F32" t="inlineStr">
+        <is>
+          <t>Sezgisel Optimizasyon</t>
+        </is>
+      </c>
+      <c r="G32" t="n">
+        <v>50</v>
+      </c>
+      <c r="H32" t="n">
         <v>40</v>
       </c>
-      <c r="E32" t="n">
+      <c r="I32" t="n">
         <v>77.06999999999999</v>
       </c>
-      <c r="F32" t="n">
-        <v>60</v>
-      </c>
-      <c r="G32" t="n">
+      <c r="J32" t="n">
+        <v>60</v>
+      </c>
+      <c r="K32" t="n">
         <v>50</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
+          <t>Mühendislik ve Doğa Bilimleri Fakültesi</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>Endüstri Mühendisliği</t>
+        </is>
+      </c>
+      <c r="C33" t="n">
+        <v>2022</v>
+      </c>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t>Guz</t>
+        </is>
+      </c>
+      <c r="E33" t="inlineStr">
+        <is>
           <t>END407S</t>
         </is>
       </c>
-      <c r="B33" t="inlineStr">
-        <is>
-          <t>Guz</t>
-        </is>
-      </c>
-      <c r="C33" t="n">
-        <v>50</v>
-      </c>
-      <c r="D33" t="n">
+      <c r="F33" t="inlineStr">
+        <is>
+          <t>Kalite Yonetim Sistemleri</t>
+        </is>
+      </c>
+      <c r="G33" t="n">
+        <v>50</v>
+      </c>
+      <c r="H33" t="n">
         <v>44</v>
       </c>
-      <c r="E33" t="n">
+      <c r="I33" t="n">
         <v>76.5</v>
       </c>
-      <c r="F33" t="n">
-        <v>60</v>
-      </c>
-      <c r="G33" t="n">
+      <c r="J33" t="n">
+        <v>60</v>
+      </c>
+      <c r="K33" t="n">
         <v>50</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
+          <t>Sağlık Bilimleri Fakültesi</t>
+        </is>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>Hemşirelik</t>
+        </is>
+      </c>
+      <c r="C34" t="n">
+        <v>2022</v>
+      </c>
+      <c r="D34" t="inlineStr">
+        <is>
+          <t>Bahar</t>
+        </is>
+      </c>
+      <c r="E34" t="inlineStr">
+        <is>
           <t>HEM402S</t>
         </is>
       </c>
-      <c r="B34" t="inlineStr">
-        <is>
-          <t>Bahar</t>
-        </is>
-      </c>
-      <c r="C34" t="n">
-        <v>50</v>
-      </c>
-      <c r="D34" t="n">
+      <c r="F34" t="inlineStr">
+        <is>
+          <t>Kadin Sagligi Hemsireliginde Guncel</t>
+        </is>
+      </c>
+      <c r="G34" t="n">
+        <v>50</v>
+      </c>
+      <c r="H34" t="n">
         <v>35</v>
       </c>
-      <c r="E34" t="n">
+      <c r="I34" t="n">
         <v>70.88</v>
       </c>
-      <c r="F34" t="n">
-        <v>60</v>
-      </c>
-      <c r="G34" t="n">
+      <c r="J34" t="n">
+        <v>60</v>
+      </c>
+      <c r="K34" t="n">
         <v>50</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
+          <t>Sağlık Bilimleri Fakültesi</t>
+        </is>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>Hemşirelik</t>
+        </is>
+      </c>
+      <c r="C35" t="n">
+        <v>2022</v>
+      </c>
+      <c r="D35" t="inlineStr">
+        <is>
+          <t>Bahar</t>
+        </is>
+      </c>
+      <c r="E35" t="inlineStr">
+        <is>
           <t>HEM404S</t>
         </is>
       </c>
-      <c r="B35" t="inlineStr">
-        <is>
-          <t>Bahar</t>
-        </is>
-      </c>
-      <c r="C35" t="n">
-        <v>50</v>
-      </c>
-      <c r="D35" t="n">
+      <c r="F35" t="inlineStr">
+        <is>
+          <t>Cocuk Sagligi Hemsireliginde Guncel</t>
+        </is>
+      </c>
+      <c r="G35" t="n">
+        <v>50</v>
+      </c>
+      <c r="H35" t="n">
         <v>39</v>
       </c>
-      <c r="E35" t="n">
+      <c r="I35" t="n">
         <v>72.75</v>
       </c>
-      <c r="F35" t="n">
-        <v>60</v>
-      </c>
-      <c r="G35" t="n">
+      <c r="J35" t="n">
+        <v>60</v>
+      </c>
+      <c r="K35" t="n">
         <v>50</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
+          <t>Sağlık Bilimleri Fakültesi</t>
+        </is>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>Hemşirelik</t>
+        </is>
+      </c>
+      <c r="C36" t="n">
+        <v>2022</v>
+      </c>
+      <c r="D36" t="inlineStr">
+        <is>
+          <t>Bahar</t>
+        </is>
+      </c>
+      <c r="E36" t="inlineStr">
+        <is>
           <t>HEM406S</t>
         </is>
       </c>
-      <c r="B36" t="inlineStr">
-        <is>
-          <t>Bahar</t>
-        </is>
-      </c>
-      <c r="C36" t="n">
-        <v>50</v>
-      </c>
-      <c r="D36" t="n">
+      <c r="F36" t="inlineStr">
+        <is>
+          <t>Ameliyathane Hemsireliginde Guncel</t>
+        </is>
+      </c>
+      <c r="G36" t="n">
+        <v>50</v>
+      </c>
+      <c r="H36" t="n">
         <v>38</v>
       </c>
-      <c r="E36" t="n">
+      <c r="I36" t="n">
         <v>71.84999999999999</v>
       </c>
-      <c r="F36" t="n">
-        <v>60</v>
-      </c>
-      <c r="G36" t="n">
+      <c r="J36" t="n">
+        <v>60</v>
+      </c>
+      <c r="K36" t="n">
         <v>50</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
+          <t>Sağlık Bilimleri Fakültesi</t>
+        </is>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>Hemşirelik</t>
+        </is>
+      </c>
+      <c r="C37" t="n">
+        <v>2022</v>
+      </c>
+      <c r="D37" t="inlineStr">
+        <is>
+          <t>Bahar</t>
+        </is>
+      </c>
+      <c r="E37" t="inlineStr">
+        <is>
           <t>HEM408S</t>
         </is>
       </c>
-      <c r="B37" t="inlineStr">
-        <is>
-          <t>Bahar</t>
-        </is>
-      </c>
-      <c r="C37" t="n">
-        <v>50</v>
-      </c>
-      <c r="D37" t="n">
+      <c r="F37" t="inlineStr">
+        <is>
+          <t>Yogun Bakim Hemsireliginde Guncel</t>
+        </is>
+      </c>
+      <c r="G37" t="n">
+        <v>50</v>
+      </c>
+      <c r="H37" t="n">
         <v>36</v>
       </c>
-      <c r="E37" t="n">
+      <c r="I37" t="n">
         <v>72.17</v>
       </c>
-      <c r="F37" t="n">
-        <v>60</v>
-      </c>
-      <c r="G37" t="n">
+      <c r="J37" t="n">
+        <v>60</v>
+      </c>
+      <c r="K37" t="n">
         <v>50</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
+          <t>Sağlık Bilimleri Fakültesi</t>
+        </is>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>Hemşirelik</t>
+        </is>
+      </c>
+      <c r="C38" t="n">
+        <v>2022</v>
+      </c>
+      <c r="D38" t="inlineStr">
+        <is>
+          <t>Guz</t>
+        </is>
+      </c>
+      <c r="E38" t="inlineStr">
+        <is>
           <t>HEM401S</t>
         </is>
       </c>
-      <c r="B38" t="inlineStr">
-        <is>
-          <t>Guz</t>
-        </is>
-      </c>
-      <c r="C38" t="n">
-        <v>50</v>
-      </c>
-      <c r="D38" t="n">
+      <c r="F38" t="inlineStr">
+        <is>
+          <t>Ileri Klinik Hemsirelik</t>
+        </is>
+      </c>
+      <c r="G38" t="n">
+        <v>50</v>
+      </c>
+      <c r="H38" t="n">
         <v>38</v>
       </c>
-      <c r="E38" t="n">
+      <c r="I38" t="n">
         <v>71.89</v>
       </c>
-      <c r="F38" t="n">
-        <v>60</v>
-      </c>
-      <c r="G38" t="n">
+      <c r="J38" t="n">
+        <v>60</v>
+      </c>
+      <c r="K38" t="n">
         <v>50</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
+          <t>Sağlık Bilimleri Fakültesi</t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>Hemşirelik</t>
+        </is>
+      </c>
+      <c r="C39" t="n">
+        <v>2022</v>
+      </c>
+      <c r="D39" t="inlineStr">
+        <is>
+          <t>Guz</t>
+        </is>
+      </c>
+      <c r="E39" t="inlineStr">
+        <is>
           <t>HEM403S</t>
         </is>
       </c>
-      <c r="B39" t="inlineStr">
-        <is>
-          <t>Guz</t>
-        </is>
-      </c>
-      <c r="C39" t="n">
-        <v>50</v>
-      </c>
-      <c r="D39" t="n">
+      <c r="F39" t="inlineStr">
+        <is>
+          <t>Psikiyatri Hemsireliginde Guncel</t>
+        </is>
+      </c>
+      <c r="G39" t="n">
+        <v>50</v>
+      </c>
+      <c r="H39" t="n">
         <v>38</v>
       </c>
-      <c r="E39" t="n">
+      <c r="I39" t="n">
         <v>71.56999999999999</v>
       </c>
-      <c r="F39" t="n">
-        <v>60</v>
-      </c>
-      <c r="G39" t="n">
+      <c r="J39" t="n">
+        <v>60</v>
+      </c>
+      <c r="K39" t="n">
         <v>50</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
+          <t>Sağlık Bilimleri Fakültesi</t>
+        </is>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>Hemşirelik</t>
+        </is>
+      </c>
+      <c r="C40" t="n">
+        <v>2022</v>
+      </c>
+      <c r="D40" t="inlineStr">
+        <is>
+          <t>Guz</t>
+        </is>
+      </c>
+      <c r="E40" t="inlineStr">
+        <is>
           <t>HEM405S</t>
         </is>
       </c>
-      <c r="B40" t="inlineStr">
-        <is>
-          <t>Guz</t>
-        </is>
-      </c>
-      <c r="C40" t="n">
-        <v>50</v>
-      </c>
-      <c r="D40" t="n">
+      <c r="F40" t="inlineStr">
+        <is>
+          <t>Onkoloji Hemsireliginde Kanit</t>
+        </is>
+      </c>
+      <c r="G40" t="n">
+        <v>50</v>
+      </c>
+      <c r="H40" t="n">
         <v>38</v>
       </c>
-      <c r="E40" t="n">
+      <c r="I40" t="n">
         <v>73.04000000000001</v>
       </c>
-      <c r="F40" t="n">
-        <v>60</v>
-      </c>
-      <c r="G40" t="n">
+      <c r="J40" t="n">
+        <v>60</v>
+      </c>
+      <c r="K40" t="n">
         <v>50</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
+          <t>Sağlık Bilimleri Fakültesi</t>
+        </is>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>Hemşirelik</t>
+        </is>
+      </c>
+      <c r="C41" t="n">
+        <v>2022</v>
+      </c>
+      <c r="D41" t="inlineStr">
+        <is>
+          <t>Guz</t>
+        </is>
+      </c>
+      <c r="E41" t="inlineStr">
+        <is>
           <t>HEM407S</t>
         </is>
       </c>
-      <c r="B41" t="inlineStr">
-        <is>
-          <t>Guz</t>
-        </is>
-      </c>
-      <c r="C41" t="n">
-        <v>50</v>
-      </c>
-      <c r="D41" t="n">
+      <c r="F41" t="inlineStr">
+        <is>
+          <t>Aile Sagligi Hemsireliginde Guncel</t>
+        </is>
+      </c>
+      <c r="G41" t="n">
+        <v>50</v>
+      </c>
+      <c r="H41" t="n">
         <v>41</v>
       </c>
-      <c r="E41" t="n">
+      <c r="I41" t="n">
         <v>75.56</v>
       </c>
-      <c r="F41" t="n">
-        <v>60</v>
-      </c>
-      <c r="G41" t="n">
+      <c r="J41" t="n">
+        <v>60</v>
+      </c>
+      <c r="K41" t="n">
         <v>50</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
+          <t>Sağlık Bilimleri Fakültesi</t>
+        </is>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>Ebelik</t>
+        </is>
+      </c>
+      <c r="C42" t="n">
+        <v>2022</v>
+      </c>
+      <c r="D42" t="inlineStr">
+        <is>
+          <t>Bahar</t>
+        </is>
+      </c>
+      <c r="E42" t="inlineStr">
+        <is>
           <t>EBE402S</t>
         </is>
       </c>
-      <c r="B42" t="inlineStr">
-        <is>
-          <t>Bahar</t>
-        </is>
-      </c>
-      <c r="C42" t="n">
-        <v>50</v>
-      </c>
-      <c r="D42" t="n">
+      <c r="F42" t="inlineStr">
+        <is>
+          <t>Infertilite Hemsireliginde Guncel</t>
+        </is>
+      </c>
+      <c r="G42" t="n">
+        <v>50</v>
+      </c>
+      <c r="H42" t="n">
         <v>33</v>
       </c>
-      <c r="E42" t="n">
+      <c r="I42" t="n">
         <v>67.81999999999999</v>
       </c>
-      <c r="F42" t="n">
-        <v>60</v>
-      </c>
-      <c r="G42" t="n">
+      <c r="J42" t="n">
+        <v>60</v>
+      </c>
+      <c r="K42" t="n">
         <v>50</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
+          <t>Sağlık Bilimleri Fakültesi</t>
+        </is>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>Ebelik</t>
+        </is>
+      </c>
+      <c r="C43" t="n">
+        <v>2022</v>
+      </c>
+      <c r="D43" t="inlineStr">
+        <is>
+          <t>Bahar</t>
+        </is>
+      </c>
+      <c r="E43" t="inlineStr">
+        <is>
           <t>EBE404S</t>
         </is>
       </c>
-      <c r="B43" t="inlineStr">
-        <is>
-          <t>Bahar</t>
-        </is>
-      </c>
-      <c r="C43" t="n">
-        <v>50</v>
-      </c>
-      <c r="D43" t="n">
+      <c r="F43" t="inlineStr">
+        <is>
+          <t>Maternal Saglik</t>
+        </is>
+      </c>
+      <c r="G43" t="n">
+        <v>50</v>
+      </c>
+      <c r="H43" t="n">
         <v>31</v>
       </c>
-      <c r="E43" t="n">
+      <c r="I43" t="n">
         <v>66.48</v>
       </c>
-      <c r="F43" t="n">
-        <v>60</v>
-      </c>
-      <c r="G43" t="n">
+      <c r="J43" t="n">
+        <v>60</v>
+      </c>
+      <c r="K43" t="n">
         <v>50</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
+          <t>Sağlık Bilimleri Fakültesi</t>
+        </is>
+      </c>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>Ebelik</t>
+        </is>
+      </c>
+      <c r="C44" t="n">
+        <v>2022</v>
+      </c>
+      <c r="D44" t="inlineStr">
+        <is>
+          <t>Bahar</t>
+        </is>
+      </c>
+      <c r="E44" t="inlineStr">
+        <is>
           <t>EBE406S</t>
         </is>
       </c>
-      <c r="B44" t="inlineStr">
-        <is>
-          <t>Bahar</t>
-        </is>
-      </c>
-      <c r="C44" t="n">
-        <v>50</v>
-      </c>
-      <c r="D44" t="n">
+      <c r="F44" t="inlineStr">
+        <is>
+          <t>Postpartum Bakim</t>
+        </is>
+      </c>
+      <c r="G44" t="n">
+        <v>50</v>
+      </c>
+      <c r="H44" t="n">
         <v>30</v>
       </c>
-      <c r="E44" t="n">
+      <c r="I44" t="n">
         <v>63.87</v>
       </c>
-      <c r="F44" t="n">
-        <v>60</v>
-      </c>
-      <c r="G44" t="n">
+      <c r="J44" t="n">
+        <v>60</v>
+      </c>
+      <c r="K44" t="n">
         <v>50</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
+          <t>Sağlık Bilimleri Fakültesi</t>
+        </is>
+      </c>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>Ebelik</t>
+        </is>
+      </c>
+      <c r="C45" t="n">
+        <v>2022</v>
+      </c>
+      <c r="D45" t="inlineStr">
+        <is>
+          <t>Bahar</t>
+        </is>
+      </c>
+      <c r="E45" t="inlineStr">
+        <is>
           <t>EBE408S</t>
         </is>
       </c>
-      <c r="B45" t="inlineStr">
-        <is>
-          <t>Bahar</t>
-        </is>
-      </c>
-      <c r="C45" t="n">
-        <v>50</v>
-      </c>
-      <c r="D45" t="n">
+      <c r="F45" t="inlineStr">
+        <is>
+          <t>Kadinlarda Onkoloji</t>
+        </is>
+      </c>
+      <c r="G45" t="n">
+        <v>50</v>
+      </c>
+      <c r="H45" t="n">
         <v>35</v>
       </c>
-      <c r="E45" t="n">
+      <c r="I45" t="n">
         <v>69.03</v>
       </c>
-      <c r="F45" t="n">
-        <v>60</v>
-      </c>
-      <c r="G45" t="n">
+      <c r="J45" t="n">
+        <v>60</v>
+      </c>
+      <c r="K45" t="n">
         <v>50</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
+          <t>Sağlık Bilimleri Fakültesi</t>
+        </is>
+      </c>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>Ebelik</t>
+        </is>
+      </c>
+      <c r="C46" t="n">
+        <v>2022</v>
+      </c>
+      <c r="D46" t="inlineStr">
+        <is>
+          <t>Guz</t>
+        </is>
+      </c>
+      <c r="E46" t="inlineStr">
+        <is>
           <t>EBE401S</t>
         </is>
       </c>
-      <c r="B46" t="inlineStr">
-        <is>
-          <t>Guz</t>
-        </is>
-      </c>
-      <c r="C46" t="n">
-        <v>50</v>
-      </c>
-      <c r="D46" t="n">
+      <c r="F46" t="inlineStr">
+        <is>
+          <t>Yuksek Riskli Gebelik Bakimi</t>
+        </is>
+      </c>
+      <c r="G46" t="n">
+        <v>50</v>
+      </c>
+      <c r="H46" t="n">
         <v>33</v>
       </c>
-      <c r="E46" t="n">
+      <c r="I46" t="n">
         <v>67.44</v>
       </c>
-      <c r="F46" t="n">
-        <v>60</v>
-      </c>
-      <c r="G46" t="n">
+      <c r="J46" t="n">
+        <v>60</v>
+      </c>
+      <c r="K46" t="n">
         <v>50</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
+          <t>Sağlık Bilimleri Fakültesi</t>
+        </is>
+      </c>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>Ebelik</t>
+        </is>
+      </c>
+      <c r="C47" t="n">
+        <v>2022</v>
+      </c>
+      <c r="D47" t="inlineStr">
+        <is>
+          <t>Guz</t>
+        </is>
+      </c>
+      <c r="E47" t="inlineStr">
+        <is>
           <t>EBE403S</t>
         </is>
       </c>
-      <c r="B47" t="inlineStr">
-        <is>
-          <t>Guz</t>
-        </is>
-      </c>
-      <c r="C47" t="n">
-        <v>50</v>
-      </c>
-      <c r="D47" t="n">
+      <c r="F47" t="inlineStr">
+        <is>
+          <t>Dogum Agi Yonetimi</t>
+        </is>
+      </c>
+      <c r="G47" t="n">
+        <v>50</v>
+      </c>
+      <c r="H47" t="n">
         <v>32</v>
       </c>
-      <c r="E47" t="n">
+      <c r="I47" t="n">
         <v>66.94</v>
       </c>
-      <c r="F47" t="n">
-        <v>60</v>
-      </c>
-      <c r="G47" t="n">
+      <c r="J47" t="n">
+        <v>60</v>
+      </c>
+      <c r="K47" t="n">
         <v>50</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
+          <t>Sağlık Bilimleri Fakültesi</t>
+        </is>
+      </c>
+      <c r="B48" t="inlineStr">
+        <is>
+          <t>Ebelik</t>
+        </is>
+      </c>
+      <c r="C48" t="n">
+        <v>2022</v>
+      </c>
+      <c r="D48" t="inlineStr">
+        <is>
+          <t>Guz</t>
+        </is>
+      </c>
+      <c r="E48" t="inlineStr">
+        <is>
           <t>EBE405S</t>
         </is>
       </c>
-      <c r="B48" t="inlineStr">
-        <is>
-          <t>Guz</t>
-        </is>
-      </c>
-      <c r="C48" t="n">
-        <v>50</v>
-      </c>
-      <c r="D48" t="n">
+      <c r="F48" t="inlineStr">
+        <is>
+          <t>Neonatal Bakim</t>
+        </is>
+      </c>
+      <c r="G48" t="n">
+        <v>50</v>
+      </c>
+      <c r="H48" t="n">
         <v>34</v>
       </c>
-      <c r="E48" t="n">
+      <c r="I48" t="n">
         <v>69.56</v>
       </c>
-      <c r="F48" t="n">
-        <v>60</v>
-      </c>
-      <c r="G48" t="n">
+      <c r="J48" t="n">
+        <v>60</v>
+      </c>
+      <c r="K48" t="n">
         <v>50</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
+          <t>Sağlık Bilimleri Fakültesi</t>
+        </is>
+      </c>
+      <c r="B49" t="inlineStr">
+        <is>
+          <t>Ebelik</t>
+        </is>
+      </c>
+      <c r="C49" t="n">
+        <v>2022</v>
+      </c>
+      <c r="D49" t="inlineStr">
+        <is>
+          <t>Guz</t>
+        </is>
+      </c>
+      <c r="E49" t="inlineStr">
+        <is>
           <t>EBE407S</t>
         </is>
       </c>
-      <c r="B49" t="inlineStr">
-        <is>
-          <t>Guz</t>
-        </is>
-      </c>
-      <c r="C49" t="n">
-        <v>50</v>
-      </c>
-      <c r="D49" t="n">
+      <c r="F49" t="inlineStr">
+        <is>
+          <t>Reproductive Saglik</t>
+        </is>
+      </c>
+      <c r="G49" t="n">
+        <v>50</v>
+      </c>
+      <c r="H49" t="n">
         <v>32</v>
       </c>
-      <c r="E49" t="n">
+      <c r="I49" t="n">
         <v>67.73</v>
       </c>
-      <c r="F49" t="n">
-        <v>60</v>
-      </c>
-      <c r="G49" t="n">
+      <c r="J49" t="n">
+        <v>60</v>
+      </c>
+      <c r="K49" t="n">
         <v>50</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
+          <t>Sağlık Bilimleri Fakültesi</t>
+        </is>
+      </c>
+      <c r="B50" t="inlineStr">
+        <is>
+          <t>Fizyoterapi ve Rehabilitasyon</t>
+        </is>
+      </c>
+      <c r="C50" t="n">
+        <v>2022</v>
+      </c>
+      <c r="D50" t="inlineStr">
+        <is>
+          <t>Bahar</t>
+        </is>
+      </c>
+      <c r="E50" t="inlineStr">
+        <is>
           <t>FTR602S</t>
         </is>
       </c>
-      <c r="B50" t="inlineStr">
-        <is>
-          <t>Bahar</t>
-        </is>
-      </c>
-      <c r="C50" t="n">
-        <v>50</v>
-      </c>
-      <c r="D50" t="n">
+      <c r="F50" t="inlineStr">
+        <is>
+          <t>Norolojik Rehabilitasyon Guncel</t>
+        </is>
+      </c>
+      <c r="G50" t="n">
+        <v>50</v>
+      </c>
+      <c r="H50" t="n">
         <v>40</v>
       </c>
-      <c r="E50" t="n">
+      <c r="I50" t="n">
         <v>74.56</v>
       </c>
-      <c r="F50" t="n">
-        <v>60</v>
-      </c>
-      <c r="G50" t="n">
+      <c r="J50" t="n">
+        <v>60</v>
+      </c>
+      <c r="K50" t="n">
         <v>50</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
+          <t>Sağlık Bilimleri Fakültesi</t>
+        </is>
+      </c>
+      <c r="B51" t="inlineStr">
+        <is>
+          <t>Fizyoterapi ve Rehabilitasyon</t>
+        </is>
+      </c>
+      <c r="C51" t="n">
+        <v>2022</v>
+      </c>
+      <c r="D51" t="inlineStr">
+        <is>
+          <t>Bahar</t>
+        </is>
+      </c>
+      <c r="E51" t="inlineStr">
+        <is>
           <t>FTR604S</t>
         </is>
       </c>
-      <c r="B51" t="inlineStr">
-        <is>
-          <t>Bahar</t>
-        </is>
-      </c>
-      <c r="C51" t="n">
-        <v>50</v>
-      </c>
-      <c r="D51" t="n">
+      <c r="F51" t="inlineStr">
+        <is>
+          <t>Ortopedik Rehabilitasyon Guncel</t>
+        </is>
+      </c>
+      <c r="G51" t="n">
+        <v>50</v>
+      </c>
+      <c r="H51" t="n">
         <v>37</v>
       </c>
-      <c r="E51" t="n">
+      <c r="I51" t="n">
         <v>70.29000000000001</v>
       </c>
-      <c r="F51" t="n">
-        <v>60</v>
-      </c>
-      <c r="G51" t="n">
+      <c r="J51" t="n">
+        <v>60</v>
+      </c>
+      <c r="K51" t="n">
         <v>50</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
+          <t>Sağlık Bilimleri Fakültesi</t>
+        </is>
+      </c>
+      <c r="B52" t="inlineStr">
+        <is>
+          <t>Fizyoterapi ve Rehabilitasyon</t>
+        </is>
+      </c>
+      <c r="C52" t="n">
+        <v>2022</v>
+      </c>
+      <c r="D52" t="inlineStr">
+        <is>
+          <t>Bahar</t>
+        </is>
+      </c>
+      <c r="E52" t="inlineStr">
+        <is>
           <t>FTR606S</t>
         </is>
       </c>
-      <c r="B52" t="inlineStr">
-        <is>
-          <t>Bahar</t>
-        </is>
-      </c>
-      <c r="C52" t="n">
-        <v>50</v>
-      </c>
-      <c r="D52" t="n">
+      <c r="F52" t="inlineStr">
+        <is>
+          <t>Onkolojik Rehabilitasyon</t>
+        </is>
+      </c>
+      <c r="G52" t="n">
+        <v>50</v>
+      </c>
+      <c r="H52" t="n">
         <v>36</v>
       </c>
-      <c r="E52" t="n">
+      <c r="I52" t="n">
         <v>70.56</v>
       </c>
-      <c r="F52" t="n">
-        <v>60</v>
-      </c>
-      <c r="G52" t="n">
+      <c r="J52" t="n">
+        <v>60</v>
+      </c>
+      <c r="K52" t="n">
         <v>50</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
+          <t>Sağlık Bilimleri Fakültesi</t>
+        </is>
+      </c>
+      <c r="B53" t="inlineStr">
+        <is>
+          <t>Fizyoterapi ve Rehabilitasyon</t>
+        </is>
+      </c>
+      <c r="C53" t="n">
+        <v>2022</v>
+      </c>
+      <c r="D53" t="inlineStr">
+        <is>
+          <t>Bahar</t>
+        </is>
+      </c>
+      <c r="E53" t="inlineStr">
+        <is>
           <t>FTR610S</t>
         </is>
       </c>
-      <c r="B53" t="inlineStr">
-        <is>
-          <t>Bahar</t>
-        </is>
-      </c>
-      <c r="C53" t="n">
-        <v>50</v>
-      </c>
-      <c r="D53" t="n">
+      <c r="F53" t="inlineStr">
+        <is>
+          <t>Geriatrik Rehabilitasyon</t>
+        </is>
+      </c>
+      <c r="G53" t="n">
+        <v>50</v>
+      </c>
+      <c r="H53" t="n">
         <v>38</v>
       </c>
-      <c r="E53" t="n">
+      <c r="I53" t="n">
         <v>71.7</v>
       </c>
-      <c r="F53" t="n">
-        <v>60</v>
-      </c>
-      <c r="G53" t="n">
+      <c r="J53" t="n">
+        <v>60</v>
+      </c>
+      <c r="K53" t="n">
         <v>50</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
+          <t>Sağlık Bilimleri Fakültesi</t>
+        </is>
+      </c>
+      <c r="B54" t="inlineStr">
+        <is>
+          <t>Fizyoterapi ve Rehabilitasyon</t>
+        </is>
+      </c>
+      <c r="C54" t="n">
+        <v>2022</v>
+      </c>
+      <c r="D54" t="inlineStr">
+        <is>
+          <t>Guz</t>
+        </is>
+      </c>
+      <c r="E54" t="inlineStr">
+        <is>
           <t>FTR608S</t>
         </is>
       </c>
-      <c r="B54" t="inlineStr">
-        <is>
-          <t>Guz</t>
-        </is>
-      </c>
-      <c r="C54" t="n">
-        <v>50</v>
-      </c>
-      <c r="D54" t="n">
+      <c r="F54" t="inlineStr">
+        <is>
+          <t>Kardiyopulmoner Rehabilitasyon</t>
+        </is>
+      </c>
+      <c r="G54" t="n">
+        <v>50</v>
+      </c>
+      <c r="H54" t="n">
         <v>32</v>
       </c>
-      <c r="E54" t="n">
+      <c r="I54" t="n">
         <v>70.44</v>
       </c>
-      <c r="F54" t="n">
-        <v>60</v>
-      </c>
-      <c r="G54" t="n">
+      <c r="J54" t="n">
+        <v>60</v>
+      </c>
+      <c r="K54" t="n">
         <v>50</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
+          <t>Sağlık Bilimleri Fakültesi</t>
+        </is>
+      </c>
+      <c r="B55" t="inlineStr">
+        <is>
+          <t>Fizyoterapi ve Rehabilitasyon</t>
+        </is>
+      </c>
+      <c r="C55" t="n">
+        <v>2022</v>
+      </c>
+      <c r="D55" t="inlineStr">
+        <is>
+          <t>Guz</t>
+        </is>
+      </c>
+      <c r="E55" t="inlineStr">
+        <is>
           <t>FTR609S</t>
         </is>
       </c>
-      <c r="B55" t="inlineStr">
-        <is>
-          <t>Guz</t>
-        </is>
-      </c>
-      <c r="C55" t="n">
-        <v>50</v>
-      </c>
-      <c r="D55" t="n">
+      <c r="F55" t="inlineStr">
+        <is>
+          <t>Pediatrik Rehabilitasyon</t>
+        </is>
+      </c>
+      <c r="G55" t="n">
+        <v>50</v>
+      </c>
+      <c r="H55" t="n">
         <v>37</v>
       </c>
-      <c r="E55" t="n">
+      <c r="I55" t="n">
         <v>72.23999999999999</v>
       </c>
-      <c r="F55" t="n">
-        <v>60</v>
-      </c>
-      <c r="G55" t="n">
+      <c r="J55" t="n">
+        <v>60</v>
+      </c>
+      <c r="K55" t="n">
         <v>50</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
+          <t>Sağlık Bilimleri Fakültesi</t>
+        </is>
+      </c>
+      <c r="B56" t="inlineStr">
+        <is>
+          <t>Fizyoterapi ve Rehabilitasyon</t>
+        </is>
+      </c>
+      <c r="C56" t="n">
+        <v>2022</v>
+      </c>
+      <c r="D56" t="inlineStr">
+        <is>
+          <t>Guz</t>
+        </is>
+      </c>
+      <c r="E56" t="inlineStr">
+        <is>
           <t>FTR611S</t>
         </is>
       </c>
-      <c r="B56" t="inlineStr">
-        <is>
-          <t>Guz</t>
-        </is>
-      </c>
-      <c r="C56" t="n">
-        <v>50</v>
-      </c>
-      <c r="D56" t="n">
+      <c r="F56" t="inlineStr">
+        <is>
+          <t>Manuel Terapi Teknikleri</t>
+        </is>
+      </c>
+      <c r="G56" t="n">
+        <v>50</v>
+      </c>
+      <c r="H56" t="n">
         <v>39</v>
       </c>
-      <c r="E56" t="n">
+      <c r="I56" t="n">
         <v>71.87</v>
       </c>
-      <c r="F56" t="n">
-        <v>60</v>
-      </c>
-      <c r="G56" t="n">
+      <c r="J56" t="n">
+        <v>60</v>
+      </c>
+      <c r="K56" t="n">
         <v>50</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
+          <t>Sağlık Bilimleri Fakültesi</t>
+        </is>
+      </c>
+      <c r="B57" t="inlineStr">
+        <is>
+          <t>Fizyoterapi ve Rehabilitasyon</t>
+        </is>
+      </c>
+      <c r="C57" t="n">
+        <v>2022</v>
+      </c>
+      <c r="D57" t="inlineStr">
+        <is>
+          <t>Guz</t>
+        </is>
+      </c>
+      <c r="E57" t="inlineStr">
+        <is>
           <t>FTR613S</t>
         </is>
       </c>
-      <c r="B57" t="inlineStr">
-        <is>
-          <t>Guz</t>
-        </is>
-      </c>
-      <c r="C57" t="n">
-        <v>50</v>
-      </c>
-      <c r="D57" t="n">
+      <c r="F57" t="inlineStr">
+        <is>
+          <t>Sportif Rehabilitasyon</t>
+        </is>
+      </c>
+      <c r="G57" t="n">
+        <v>50</v>
+      </c>
+      <c r="H57" t="n">
         <v>41</v>
       </c>
-      <c r="E57" t="n">
+      <c r="I57" t="n">
         <v>73.44</v>
       </c>
-      <c r="F57" t="n">
-        <v>60</v>
-      </c>
-      <c r="G57" t="n">
+      <c r="J57" t="n">
+        <v>60</v>
+      </c>
+      <c r="K57" t="n">
         <v>50</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
+          <t>Güzel Sanatlar Fakültesi</t>
+        </is>
+      </c>
+      <c r="B58" t="inlineStr">
+        <is>
+          <t>Gastronomi</t>
+        </is>
+      </c>
+      <c r="C58" t="n">
+        <v>2022</v>
+      </c>
+      <c r="D58" t="inlineStr">
+        <is>
+          <t>Bahar</t>
+        </is>
+      </c>
+      <c r="E58" t="inlineStr">
+        <is>
           <t>GAS402S</t>
         </is>
       </c>
-      <c r="B58" t="inlineStr">
-        <is>
-          <t>Bahar</t>
-        </is>
-      </c>
-      <c r="C58" t="n">
-        <v>50</v>
-      </c>
-      <c r="D58" t="n">
+      <c r="F58" t="inlineStr">
+        <is>
+          <t>Fermentasyon ve Mutfak Kimyasi</t>
+        </is>
+      </c>
+      <c r="G58" t="n">
+        <v>50</v>
+      </c>
+      <c r="H58" t="n">
         <v>24</v>
       </c>
-      <c r="E58" t="n">
+      <c r="I58" t="n">
         <v>62.61</v>
       </c>
-      <c r="F58" t="n">
-        <v>60</v>
-      </c>
-      <c r="G58" t="n">
+      <c r="J58" t="n">
+        <v>60</v>
+      </c>
+      <c r="K58" t="n">
         <v>50</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
+          <t>Güzel Sanatlar Fakültesi</t>
+        </is>
+      </c>
+      <c r="B59" t="inlineStr">
+        <is>
+          <t>Gastronomi</t>
+        </is>
+      </c>
+      <c r="C59" t="n">
+        <v>2022</v>
+      </c>
+      <c r="D59" t="inlineStr">
+        <is>
+          <t>Bahar</t>
+        </is>
+      </c>
+      <c r="E59" t="inlineStr">
+        <is>
           <t>GAS404S</t>
         </is>
       </c>
-      <c r="B59" t="inlineStr">
-        <is>
-          <t>Bahar</t>
-        </is>
-      </c>
-      <c r="C59" t="n">
-        <v>50</v>
-      </c>
-      <c r="D59" t="n">
+      <c r="F59" t="inlineStr">
+        <is>
+          <t>Pastane ve Firinci Sanatlari</t>
+        </is>
+      </c>
+      <c r="G59" t="n">
+        <v>50</v>
+      </c>
+      <c r="H59" t="n">
         <v>24</v>
       </c>
-      <c r="E59" t="n">
+      <c r="I59" t="n">
         <v>61.68</v>
       </c>
-      <c r="F59" t="n">
-        <v>60</v>
-      </c>
-      <c r="G59" t="n">
+      <c r="J59" t="n">
+        <v>60</v>
+      </c>
+      <c r="K59" t="n">
         <v>50</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
+          <t>Güzel Sanatlar Fakültesi</t>
+        </is>
+      </c>
+      <c r="B60" t="inlineStr">
+        <is>
+          <t>Gastronomi</t>
+        </is>
+      </c>
+      <c r="C60" t="n">
+        <v>2022</v>
+      </c>
+      <c r="D60" t="inlineStr">
+        <is>
+          <t>Bahar</t>
+        </is>
+      </c>
+      <c r="E60" t="inlineStr">
+        <is>
           <t>GAS406S</t>
         </is>
       </c>
-      <c r="B60" t="inlineStr">
-        <is>
-          <t>Bahar</t>
-        </is>
-      </c>
-      <c r="C60" t="n">
-        <v>50</v>
-      </c>
-      <c r="D60" t="n">
+      <c r="F60" t="inlineStr">
+        <is>
+          <t>Gida Stili ve Fotografciligi</t>
+        </is>
+      </c>
+      <c r="G60" t="n">
+        <v>50</v>
+      </c>
+      <c r="H60" t="n">
         <v>23</v>
       </c>
-      <c r="E60" t="n">
+      <c r="I60" t="n">
         <v>60.83</v>
       </c>
-      <c r="F60" t="n">
-        <v>60</v>
-      </c>
-      <c r="G60" t="n">
+      <c r="J60" t="n">
+        <v>60</v>
+      </c>
+      <c r="K60" t="n">
         <v>50</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
+          <t>Güzel Sanatlar Fakültesi</t>
+        </is>
+      </c>
+      <c r="B61" t="inlineStr">
+        <is>
+          <t>Gastronomi</t>
+        </is>
+      </c>
+      <c r="C61" t="n">
+        <v>2022</v>
+      </c>
+      <c r="D61" t="inlineStr">
+        <is>
+          <t>Bahar</t>
+        </is>
+      </c>
+      <c r="E61" t="inlineStr">
+        <is>
           <t>GAS408S</t>
         </is>
       </c>
-      <c r="B61" t="inlineStr">
-        <is>
-          <t>Bahar</t>
-        </is>
-      </c>
-      <c r="C61" t="n">
-        <v>50</v>
-      </c>
-      <c r="D61" t="n">
+      <c r="F61" t="inlineStr">
+        <is>
+          <t>Gastronomi Turizmi</t>
+        </is>
+      </c>
+      <c r="G61" t="n">
+        <v>50</v>
+      </c>
+      <c r="H61" t="n">
         <v>22</v>
       </c>
-      <c r="E61" t="n">
+      <c r="I61" t="n">
         <v>60.34</v>
       </c>
-      <c r="F61" t="n">
-        <v>60</v>
-      </c>
-      <c r="G61" t="n">
+      <c r="J61" t="n">
+        <v>60</v>
+      </c>
+      <c r="K61" t="n">
         <v>50</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
+          <t>Güzel Sanatlar Fakültesi</t>
+        </is>
+      </c>
+      <c r="B62" t="inlineStr">
+        <is>
+          <t>Gastronomi</t>
+        </is>
+      </c>
+      <c r="C62" t="n">
+        <v>2022</v>
+      </c>
+      <c r="D62" t="inlineStr">
+        <is>
+          <t>Guz</t>
+        </is>
+      </c>
+      <c r="E62" t="inlineStr">
+        <is>
           <t>GAS401S</t>
         </is>
       </c>
-      <c r="B62" t="inlineStr">
-        <is>
-          <t>Guz</t>
-        </is>
-      </c>
-      <c r="C62" t="n">
-        <v>50</v>
-      </c>
-      <c r="D62" t="n">
+      <c r="F62" t="inlineStr">
+        <is>
+          <t>Molekuler Gastronomi</t>
+        </is>
+      </c>
+      <c r="G62" t="n">
+        <v>50</v>
+      </c>
+      <c r="H62" t="n">
         <v>25</v>
       </c>
-      <c r="E62" t="n">
+      <c r="I62" t="n">
         <v>63.49</v>
       </c>
-      <c r="F62" t="n">
-        <v>60</v>
-      </c>
-      <c r="G62" t="n">
+      <c r="J62" t="n">
+        <v>60</v>
+      </c>
+      <c r="K62" t="n">
         <v>50</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
+          <t>Güzel Sanatlar Fakültesi</t>
+        </is>
+      </c>
+      <c r="B63" t="inlineStr">
+        <is>
+          <t>Gastronomi</t>
+        </is>
+      </c>
+      <c r="C63" t="n">
+        <v>2022</v>
+      </c>
+      <c r="D63" t="inlineStr">
+        <is>
+          <t>Guz</t>
+        </is>
+      </c>
+      <c r="E63" t="inlineStr">
+        <is>
           <t>GAS403S</t>
         </is>
       </c>
-      <c r="B63" t="inlineStr">
-        <is>
-          <t>Guz</t>
-        </is>
-      </c>
-      <c r="C63" t="n">
-        <v>50</v>
-      </c>
-      <c r="D63" t="n">
+      <c r="F63" t="inlineStr">
+        <is>
+          <t>Dunya Mutfaklari</t>
+        </is>
+      </c>
+      <c r="G63" t="n">
+        <v>50</v>
+      </c>
+      <c r="H63" t="n">
         <v>26</v>
       </c>
-      <c r="E63" t="n">
+      <c r="I63" t="n">
         <v>63.39</v>
       </c>
-      <c r="F63" t="n">
-        <v>60</v>
-      </c>
-      <c r="G63" t="n">
+      <c r="J63" t="n">
+        <v>60</v>
+      </c>
+      <c r="K63" t="n">
         <v>50</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
+          <t>Güzel Sanatlar Fakültesi</t>
+        </is>
+      </c>
+      <c r="B64" t="inlineStr">
+        <is>
+          <t>Gastronomi</t>
+        </is>
+      </c>
+      <c r="C64" t="n">
+        <v>2022</v>
+      </c>
+      <c r="D64" t="inlineStr">
+        <is>
+          <t>Guz</t>
+        </is>
+      </c>
+      <c r="E64" t="inlineStr">
+        <is>
           <t>GAS405S</t>
         </is>
       </c>
-      <c r="B64" t="inlineStr">
-        <is>
-          <t>Guz</t>
-        </is>
-      </c>
-      <c r="C64" t="n">
-        <v>50</v>
-      </c>
-      <c r="D64" t="n">
+      <c r="F64" t="inlineStr">
+        <is>
+          <t>Seker ve Cikolata Sanatlari</t>
+        </is>
+      </c>
+      <c r="G64" t="n">
+        <v>50</v>
+      </c>
+      <c r="H64" t="n">
         <v>22</v>
       </c>
-      <c r="E64" t="n">
+      <c r="I64" t="n">
         <v>60.08</v>
       </c>
-      <c r="F64" t="n">
-        <v>60</v>
-      </c>
-      <c r="G64" t="n">
+      <c r="J64" t="n">
+        <v>60</v>
+      </c>
+      <c r="K64" t="n">
         <v>50</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
+          <t>Güzel Sanatlar Fakültesi</t>
+        </is>
+      </c>
+      <c r="B65" t="inlineStr">
+        <is>
+          <t>Gastronomi</t>
+        </is>
+      </c>
+      <c r="C65" t="n">
+        <v>2022</v>
+      </c>
+      <c r="D65" t="inlineStr">
+        <is>
+          <t>Guz</t>
+        </is>
+      </c>
+      <c r="E65" t="inlineStr">
+        <is>
           <t>GAS407S</t>
         </is>
       </c>
-      <c r="B65" t="inlineStr">
-        <is>
-          <t>Guz</t>
-        </is>
-      </c>
-      <c r="C65" t="n">
-        <v>50</v>
-      </c>
-      <c r="D65" t="n">
+      <c r="F65" t="inlineStr">
+        <is>
+          <t>Restoran Yonetimi</t>
+        </is>
+      </c>
+      <c r="G65" t="n">
+        <v>50</v>
+      </c>
+      <c r="H65" t="n">
         <v>30</v>
       </c>
-      <c r="E65" t="n">
+      <c r="I65" t="n">
         <v>63.33</v>
       </c>
-      <c r="F65" t="n">
-        <v>60</v>
-      </c>
-      <c r="G65" t="n">
+      <c r="J65" t="n">
+        <v>60</v>
+      </c>
+      <c r="K65" t="n">
         <v>50</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
+          <t>İlahiyat Fakültesi</t>
+        </is>
+      </c>
+      <c r="B66" t="inlineStr">
+        <is>
+          <t>İlahiyat</t>
+        </is>
+      </c>
+      <c r="C66" t="n">
+        <v>2022</v>
+      </c>
+      <c r="D66" t="inlineStr">
+        <is>
+          <t>Bahar</t>
+        </is>
+      </c>
+      <c r="E66" t="inlineStr">
+        <is>
           <t>ILH201S</t>
         </is>
       </c>
-      <c r="B66" t="inlineStr">
-        <is>
-          <t>Bahar</t>
-        </is>
-      </c>
-      <c r="C66" t="n">
-        <v>50</v>
-      </c>
-      <c r="D66" t="n">
+      <c r="F66" t="inlineStr">
+        <is>
+          <t>Kuran Yorumlari ve Tefsir</t>
+        </is>
+      </c>
+      <c r="G66" t="n">
+        <v>50</v>
+      </c>
+      <c r="H66" t="n">
         <v>26</v>
       </c>
-      <c r="E66" t="n">
+      <c r="I66" t="n">
         <v>63.87</v>
       </c>
-      <c r="F66" t="n">
-        <v>60</v>
-      </c>
-      <c r="G66" t="n">
+      <c r="J66" t="n">
+        <v>60</v>
+      </c>
+      <c r="K66" t="n">
         <v>50</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
+          <t>İlahiyat Fakültesi</t>
+        </is>
+      </c>
+      <c r="B67" t="inlineStr">
+        <is>
+          <t>İlahiyat</t>
+        </is>
+      </c>
+      <c r="C67" t="n">
+        <v>2022</v>
+      </c>
+      <c r="D67" t="inlineStr">
+        <is>
+          <t>Bahar</t>
+        </is>
+      </c>
+      <c r="E67" t="inlineStr">
+        <is>
           <t>ILH202S</t>
         </is>
       </c>
-      <c r="B67" t="inlineStr">
-        <is>
-          <t>Bahar</t>
-        </is>
-      </c>
-      <c r="C67" t="n">
-        <v>50</v>
-      </c>
-      <c r="D67" t="n">
+      <c r="F67" t="inlineStr">
+        <is>
+          <t>Islam Felsefesi</t>
+        </is>
+      </c>
+      <c r="G67" t="n">
+        <v>50</v>
+      </c>
+      <c r="H67" t="n">
         <v>30</v>
       </c>
-      <c r="E67" t="n">
+      <c r="I67" t="n">
         <v>64.98999999999999</v>
       </c>
-      <c r="F67" t="n">
-        <v>60</v>
-      </c>
-      <c r="G67" t="n">
+      <c r="J67" t="n">
+        <v>60</v>
+      </c>
+      <c r="K67" t="n">
         <v>50</v>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
+          <t>İlahiyat Fakültesi</t>
+        </is>
+      </c>
+      <c r="B68" t="inlineStr">
+        <is>
+          <t>İlahiyat</t>
+        </is>
+      </c>
+      <c r="C68" t="n">
+        <v>2022</v>
+      </c>
+      <c r="D68" t="inlineStr">
+        <is>
+          <t>Bahar</t>
+        </is>
+      </c>
+      <c r="E68" t="inlineStr">
+        <is>
           <t>ILH203S</t>
         </is>
       </c>
-      <c r="B68" t="inlineStr">
-        <is>
-          <t>Bahar</t>
-        </is>
-      </c>
-      <c r="C68" t="n">
-        <v>50</v>
-      </c>
-      <c r="D68" t="n">
+      <c r="F68" t="inlineStr">
+        <is>
+          <t>Din Egitimi Yontemleri</t>
+        </is>
+      </c>
+      <c r="G68" t="n">
+        <v>50</v>
+      </c>
+      <c r="H68" t="n">
         <v>29</v>
       </c>
-      <c r="E68" t="n">
+      <c r="I68" t="n">
         <v>64.37</v>
       </c>
-      <c r="F68" t="n">
-        <v>60</v>
-      </c>
-      <c r="G68" t="n">
+      <c r="J68" t="n">
+        <v>60</v>
+      </c>
+      <c r="K68" t="n">
         <v>50</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
+          <t>İlahiyat Fakültesi</t>
+        </is>
+      </c>
+      <c r="B69" t="inlineStr">
+        <is>
+          <t>İlahiyat</t>
+        </is>
+      </c>
+      <c r="C69" t="n">
+        <v>2022</v>
+      </c>
+      <c r="D69" t="inlineStr">
+        <is>
+          <t>Bahar</t>
+        </is>
+      </c>
+      <c r="E69" t="inlineStr">
+        <is>
           <t>ILH204S</t>
         </is>
       </c>
-      <c r="B69" t="inlineStr">
-        <is>
-          <t>Bahar</t>
-        </is>
-      </c>
-      <c r="C69" t="n">
-        <v>50</v>
-      </c>
-      <c r="D69" t="n">
+      <c r="F69" t="inlineStr">
+        <is>
+          <t>Tasavvuf ve Manevi Hayat</t>
+        </is>
+      </c>
+      <c r="G69" t="n">
+        <v>50</v>
+      </c>
+      <c r="H69" t="n">
         <v>30</v>
       </c>
-      <c r="E69" t="n">
+      <c r="I69" t="n">
         <v>67.33</v>
       </c>
-      <c r="F69" t="n">
-        <v>60</v>
-      </c>
-      <c r="G69" t="n">
+      <c r="J69" t="n">
+        <v>60</v>
+      </c>
+      <c r="K69" t="n">
         <v>50</v>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
+          <t>İlahiyat Fakültesi</t>
+        </is>
+      </c>
+      <c r="B70" t="inlineStr">
+        <is>
+          <t>İlahiyat</t>
+        </is>
+      </c>
+      <c r="C70" t="n">
+        <v>2022</v>
+      </c>
+      <c r="D70" t="inlineStr">
+        <is>
+          <t>Guz</t>
+        </is>
+      </c>
+      <c r="E70" t="inlineStr">
+        <is>
           <t>ILH109S</t>
         </is>
       </c>
-      <c r="B70" t="inlineStr">
-        <is>
-          <t>Guz</t>
-        </is>
-      </c>
-      <c r="C70" t="n">
-        <v>50</v>
-      </c>
-      <c r="D70" t="n">
+      <c r="F70" t="inlineStr">
+        <is>
+          <t>Islami Etik ve Ahlak</t>
+        </is>
+      </c>
+      <c r="G70" t="n">
+        <v>50</v>
+      </c>
+      <c r="H70" t="n">
         <v>31</v>
       </c>
-      <c r="E70" t="n">
+      <c r="I70" t="n">
         <v>67.47</v>
       </c>
-      <c r="F70" t="n">
-        <v>60</v>
-      </c>
-      <c r="G70" t="n">
+      <c r="J70" t="n">
+        <v>60</v>
+      </c>
+      <c r="K70" t="n">
         <v>50</v>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
+          <t>İlahiyat Fakültesi</t>
+        </is>
+      </c>
+      <c r="B71" t="inlineStr">
+        <is>
+          <t>İlahiyat</t>
+        </is>
+      </c>
+      <c r="C71" t="n">
+        <v>2022</v>
+      </c>
+      <c r="D71" t="inlineStr">
+        <is>
+          <t>Guz</t>
+        </is>
+      </c>
+      <c r="E71" t="inlineStr">
+        <is>
           <t>ILH110S</t>
         </is>
       </c>
-      <c r="B71" t="inlineStr">
-        <is>
-          <t>Guz</t>
-        </is>
-      </c>
-      <c r="C71" t="n">
-        <v>50</v>
-      </c>
-      <c r="D71" t="n">
+      <c r="F71" t="inlineStr">
+        <is>
+          <t>Karsilastirmali Dinler Tarihi</t>
+        </is>
+      </c>
+      <c r="G71" t="n">
+        <v>50</v>
+      </c>
+      <c r="H71" t="n">
         <v>30</v>
       </c>
-      <c r="E71" t="n">
+      <c r="I71" t="n">
         <v>63.94</v>
       </c>
-      <c r="F71" t="n">
-        <v>60</v>
-      </c>
-      <c r="G71" t="n">
+      <c r="J71" t="n">
+        <v>60</v>
+      </c>
+      <c r="K71" t="n">
         <v>50</v>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
+          <t>İlahiyat Fakültesi</t>
+        </is>
+      </c>
+      <c r="B72" t="inlineStr">
+        <is>
+          <t>İlahiyat</t>
+        </is>
+      </c>
+      <c r="C72" t="n">
+        <v>2022</v>
+      </c>
+      <c r="D72" t="inlineStr">
+        <is>
+          <t>Guz</t>
+        </is>
+      </c>
+      <c r="E72" t="inlineStr">
+        <is>
           <t>ILH111S</t>
         </is>
       </c>
-      <c r="B72" t="inlineStr">
-        <is>
-          <t>Guz</t>
-        </is>
-      </c>
-      <c r="C72" t="n">
-        <v>50</v>
-      </c>
-      <c r="D72" t="n">
+      <c r="F72" t="inlineStr">
+        <is>
+          <t>Hadis Ilimleri Secmeli</t>
+        </is>
+      </c>
+      <c r="G72" t="n">
+        <v>50</v>
+      </c>
+      <c r="H72" t="n">
         <v>32</v>
       </c>
-      <c r="E72" t="n">
+      <c r="I72" t="n">
         <v>66.19</v>
       </c>
-      <c r="F72" t="n">
-        <v>60</v>
-      </c>
-      <c r="G72" t="n">
+      <c r="J72" t="n">
+        <v>60</v>
+      </c>
+      <c r="K72" t="n">
         <v>50</v>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
+          <t>İlahiyat Fakültesi</t>
+        </is>
+      </c>
+      <c r="B73" t="inlineStr">
+        <is>
+          <t>İlahiyat</t>
+        </is>
+      </c>
+      <c r="C73" t="n">
+        <v>2022</v>
+      </c>
+      <c r="D73" t="inlineStr">
+        <is>
+          <t>Guz</t>
+        </is>
+      </c>
+      <c r="E73" t="inlineStr">
+        <is>
           <t>ILH112S</t>
         </is>
       </c>
-      <c r="B73" t="inlineStr">
-        <is>
-          <t>Guz</t>
-        </is>
-      </c>
-      <c r="C73" t="n">
-        <v>50</v>
-      </c>
-      <c r="D73" t="n">
+      <c r="F73" t="inlineStr">
+        <is>
+          <t>Kelam Tarihi Secmeli</t>
+        </is>
+      </c>
+      <c r="G73" t="n">
+        <v>50</v>
+      </c>
+      <c r="H73" t="n">
         <v>28</v>
       </c>
-      <c r="E73" t="n">
+      <c r="I73" t="n">
         <v>66.44</v>
       </c>
-      <c r="F73" t="n">
-        <v>60</v>
-      </c>
-      <c r="G73" t="n">
+      <c r="J73" t="n">
+        <v>60</v>
+      </c>
+      <c r="K73" t="n">
         <v>50</v>
       </c>
     </row>

--- a/data/kriter_veri_seti_2022.xlsx
+++ b/data/kriter_veri_seti_2022.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K73"/>
+  <dimension ref="A1:O73"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -472,6 +472,26 @@
           <t>kayitli_ogrenci</t>
         </is>
       </c>
+      <c r="L1" t="inlineStr">
+        <is>
+          <t>katilim_sayisi</t>
+        </is>
+      </c>
+      <c r="M1" t="inlineStr">
+        <is>
+          <t>toplam_hafta</t>
+        </is>
+      </c>
+      <c r="N1" t="inlineStr">
+        <is>
+          <t>katilim_yuzdesi</t>
+        </is>
+      </c>
+      <c r="O1" t="inlineStr">
+        <is>
+          <t>devamsiz_ogrenci_sayisi</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -517,6 +537,18 @@
       <c r="K2" t="n">
         <v>50</v>
       </c>
+      <c r="L2" t="n">
+        <v>11.98</v>
+      </c>
+      <c r="M2" t="n">
+        <v>14</v>
+      </c>
+      <c r="N2" t="n">
+        <v>85.59</v>
+      </c>
+      <c r="O2" t="n">
+        <v>3</v>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -562,6 +594,18 @@
       <c r="K3" t="n">
         <v>50</v>
       </c>
+      <c r="L3" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="M3" t="n">
+        <v>14</v>
+      </c>
+      <c r="N3" t="n">
+        <v>89.3</v>
+      </c>
+      <c r="O3" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -607,6 +651,18 @@
       <c r="K4" t="n">
         <v>50</v>
       </c>
+      <c r="L4" t="n">
+        <v>11.76</v>
+      </c>
+      <c r="M4" t="n">
+        <v>14</v>
+      </c>
+      <c r="N4" t="n">
+        <v>84.01000000000001</v>
+      </c>
+      <c r="O4" t="n">
+        <v>6</v>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -652,6 +708,18 @@
       <c r="K5" t="n">
         <v>50</v>
       </c>
+      <c r="L5" t="n">
+        <v>12.1</v>
+      </c>
+      <c r="M5" t="n">
+        <v>14</v>
+      </c>
+      <c r="N5" t="n">
+        <v>86.44</v>
+      </c>
+      <c r="O5" t="n">
+        <v>3</v>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -697,6 +765,18 @@
       <c r="K6" t="n">
         <v>50</v>
       </c>
+      <c r="L6" t="n">
+        <v>11.8</v>
+      </c>
+      <c r="M6" t="n">
+        <v>14</v>
+      </c>
+      <c r="N6" t="n">
+        <v>84.29000000000001</v>
+      </c>
+      <c r="O6" t="n">
+        <v>7</v>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -742,6 +822,18 @@
       <c r="K7" t="n">
         <v>50</v>
       </c>
+      <c r="L7" t="n">
+        <v>12.18</v>
+      </c>
+      <c r="M7" t="n">
+        <v>14</v>
+      </c>
+      <c r="N7" t="n">
+        <v>87.01000000000001</v>
+      </c>
+      <c r="O7" t="n">
+        <v>2</v>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -787,6 +879,18 @@
       <c r="K8" t="n">
         <v>50</v>
       </c>
+      <c r="L8" t="n">
+        <v>12.02</v>
+      </c>
+      <c r="M8" t="n">
+        <v>14</v>
+      </c>
+      <c r="N8" t="n">
+        <v>85.87</v>
+      </c>
+      <c r="O8" t="n">
+        <v>5</v>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -832,6 +936,18 @@
       <c r="K9" t="n">
         <v>50</v>
       </c>
+      <c r="L9" t="n">
+        <v>12.32</v>
+      </c>
+      <c r="M9" t="n">
+        <v>14</v>
+      </c>
+      <c r="N9" t="n">
+        <v>88.01000000000001</v>
+      </c>
+      <c r="O9" t="n">
+        <v>2</v>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -877,6 +993,18 @@
       <c r="K10" t="n">
         <v>50</v>
       </c>
+      <c r="L10" t="n">
+        <v>11.58</v>
+      </c>
+      <c r="M10" t="n">
+        <v>14</v>
+      </c>
+      <c r="N10" t="n">
+        <v>82.72</v>
+      </c>
+      <c r="O10" t="n">
+        <v>4</v>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -922,6 +1050,18 @@
       <c r="K11" t="n">
         <v>50</v>
       </c>
+      <c r="L11" t="n">
+        <v>11.66</v>
+      </c>
+      <c r="M11" t="n">
+        <v>14</v>
+      </c>
+      <c r="N11" t="n">
+        <v>83.29000000000001</v>
+      </c>
+      <c r="O11" t="n">
+        <v>2</v>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -967,6 +1107,18 @@
       <c r="K12" t="n">
         <v>50</v>
       </c>
+      <c r="L12" t="n">
+        <v>11.6</v>
+      </c>
+      <c r="M12" t="n">
+        <v>14</v>
+      </c>
+      <c r="N12" t="n">
+        <v>82.86</v>
+      </c>
+      <c r="O12" t="n">
+        <v>4</v>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -1012,6 +1164,18 @@
       <c r="K13" t="n">
         <v>50</v>
       </c>
+      <c r="L13" t="n">
+        <v>11.8</v>
+      </c>
+      <c r="M13" t="n">
+        <v>14</v>
+      </c>
+      <c r="N13" t="n">
+        <v>84.3</v>
+      </c>
+      <c r="O13" t="n">
+        <v>4</v>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -1057,6 +1221,18 @@
       <c r="K14" t="n">
         <v>50</v>
       </c>
+      <c r="L14" t="n">
+        <v>11.92</v>
+      </c>
+      <c r="M14" t="n">
+        <v>14</v>
+      </c>
+      <c r="N14" t="n">
+        <v>85.15000000000001</v>
+      </c>
+      <c r="O14" t="n">
+        <v>4</v>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -1102,6 +1278,18 @@
       <c r="K15" t="n">
         <v>50</v>
       </c>
+      <c r="L15" t="n">
+        <v>11.7</v>
+      </c>
+      <c r="M15" t="n">
+        <v>14</v>
+      </c>
+      <c r="N15" t="n">
+        <v>83.58</v>
+      </c>
+      <c r="O15" t="n">
+        <v>4</v>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
@@ -1147,6 +1335,18 @@
       <c r="K16" t="n">
         <v>50</v>
       </c>
+      <c r="L16" t="n">
+        <v>12.26</v>
+      </c>
+      <c r="M16" t="n">
+        <v>14</v>
+      </c>
+      <c r="N16" t="n">
+        <v>87.58</v>
+      </c>
+      <c r="O16" t="n">
+        <v>2</v>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
@@ -1192,6 +1392,18 @@
       <c r="K17" t="n">
         <v>50</v>
       </c>
+      <c r="L17" t="n">
+        <v>11.9</v>
+      </c>
+      <c r="M17" t="n">
+        <v>14</v>
+      </c>
+      <c r="N17" t="n">
+        <v>85.01000000000001</v>
+      </c>
+      <c r="O17" t="n">
+        <v>2</v>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
@@ -1237,6 +1449,18 @@
       <c r="K18" t="n">
         <v>50</v>
       </c>
+      <c r="L18" t="n">
+        <v>11.82</v>
+      </c>
+      <c r="M18" t="n">
+        <v>14</v>
+      </c>
+      <c r="N18" t="n">
+        <v>84.44</v>
+      </c>
+      <c r="O18" t="n">
+        <v>3</v>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
@@ -1282,6 +1506,18 @@
       <c r="K19" t="n">
         <v>50</v>
       </c>
+      <c r="L19" t="n">
+        <v>11.84</v>
+      </c>
+      <c r="M19" t="n">
+        <v>14</v>
+      </c>
+      <c r="N19" t="n">
+        <v>84.58</v>
+      </c>
+      <c r="O19" t="n">
+        <v>3</v>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
@@ -1327,6 +1563,18 @@
       <c r="K20" t="n">
         <v>50</v>
       </c>
+      <c r="L20" t="n">
+        <v>12.04</v>
+      </c>
+      <c r="M20" t="n">
+        <v>14</v>
+      </c>
+      <c r="N20" t="n">
+        <v>86.01000000000001</v>
+      </c>
+      <c r="O20" t="n">
+        <v>4</v>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
@@ -1372,6 +1620,18 @@
       <c r="K21" t="n">
         <v>50</v>
       </c>
+      <c r="L21" t="n">
+        <v>12.14</v>
+      </c>
+      <c r="M21" t="n">
+        <v>14</v>
+      </c>
+      <c r="N21" t="n">
+        <v>86.72</v>
+      </c>
+      <c r="O21" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
@@ -1417,6 +1677,18 @@
       <c r="K22" t="n">
         <v>50</v>
       </c>
+      <c r="L22" t="n">
+        <v>11.82</v>
+      </c>
+      <c r="M22" t="n">
+        <v>14</v>
+      </c>
+      <c r="N22" t="n">
+        <v>84.43000000000001</v>
+      </c>
+      <c r="O22" t="n">
+        <v>4</v>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
@@ -1462,6 +1734,18 @@
       <c r="K23" t="n">
         <v>50</v>
       </c>
+      <c r="L23" t="n">
+        <v>12.52</v>
+      </c>
+      <c r="M23" t="n">
+        <v>14</v>
+      </c>
+      <c r="N23" t="n">
+        <v>89.43000000000001</v>
+      </c>
+      <c r="O23" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
@@ -1507,6 +1791,18 @@
       <c r="K24" t="n">
         <v>50</v>
       </c>
+      <c r="L24" t="n">
+        <v>11.92</v>
+      </c>
+      <c r="M24" t="n">
+        <v>14</v>
+      </c>
+      <c r="N24" t="n">
+        <v>85.15000000000001</v>
+      </c>
+      <c r="O24" t="n">
+        <v>4</v>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
@@ -1552,6 +1848,18 @@
       <c r="K25" t="n">
         <v>50</v>
       </c>
+      <c r="L25" t="n">
+        <v>12.44</v>
+      </c>
+      <c r="M25" t="n">
+        <v>14</v>
+      </c>
+      <c r="N25" t="n">
+        <v>88.87</v>
+      </c>
+      <c r="O25" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
@@ -1597,6 +1905,18 @@
       <c r="K26" t="n">
         <v>50</v>
       </c>
+      <c r="L26" t="n">
+        <v>11.78</v>
+      </c>
+      <c r="M26" t="n">
+        <v>14</v>
+      </c>
+      <c r="N26" t="n">
+        <v>84.16</v>
+      </c>
+      <c r="O26" t="n">
+        <v>6</v>
+      </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
@@ -1642,6 +1962,18 @@
       <c r="K27" t="n">
         <v>50</v>
       </c>
+      <c r="L27" t="n">
+        <v>12.22</v>
+      </c>
+      <c r="M27" t="n">
+        <v>14</v>
+      </c>
+      <c r="N27" t="n">
+        <v>87.29000000000001</v>
+      </c>
+      <c r="O27" t="n">
+        <v>3</v>
+      </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
@@ -1687,6 +2019,18 @@
       <c r="K28" t="n">
         <v>50</v>
       </c>
+      <c r="L28" t="n">
+        <v>11.74</v>
+      </c>
+      <c r="M28" t="n">
+        <v>14</v>
+      </c>
+      <c r="N28" t="n">
+        <v>83.86</v>
+      </c>
+      <c r="O28" t="n">
+        <v>4</v>
+      </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
@@ -1732,6 +2076,18 @@
       <c r="K29" t="n">
         <v>50</v>
       </c>
+      <c r="L29" t="n">
+        <v>12.12</v>
+      </c>
+      <c r="M29" t="n">
+        <v>14</v>
+      </c>
+      <c r="N29" t="n">
+        <v>86.58</v>
+      </c>
+      <c r="O29" t="n">
+        <v>3</v>
+      </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
@@ -1777,6 +2133,18 @@
       <c r="K30" t="n">
         <v>50</v>
       </c>
+      <c r="L30" t="n">
+        <v>11.92</v>
+      </c>
+      <c r="M30" t="n">
+        <v>14</v>
+      </c>
+      <c r="N30" t="n">
+        <v>85.15000000000001</v>
+      </c>
+      <c r="O30" t="n">
+        <v>6</v>
+      </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
@@ -1822,6 +2190,18 @@
       <c r="K31" t="n">
         <v>50</v>
       </c>
+      <c r="L31" t="n">
+        <v>11.9</v>
+      </c>
+      <c r="M31" t="n">
+        <v>14</v>
+      </c>
+      <c r="N31" t="n">
+        <v>85.01000000000001</v>
+      </c>
+      <c r="O31" t="n">
+        <v>3</v>
+      </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
@@ -1867,6 +2247,18 @@
       <c r="K32" t="n">
         <v>50</v>
       </c>
+      <c r="L32" t="n">
+        <v>11.84</v>
+      </c>
+      <c r="M32" t="n">
+        <v>14</v>
+      </c>
+      <c r="N32" t="n">
+        <v>84.56999999999999</v>
+      </c>
+      <c r="O32" t="n">
+        <v>5</v>
+      </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
@@ -1912,6 +2304,18 @@
       <c r="K33" t="n">
         <v>50</v>
       </c>
+      <c r="L33" t="n">
+        <v>11.88</v>
+      </c>
+      <c r="M33" t="n">
+        <v>14</v>
+      </c>
+      <c r="N33" t="n">
+        <v>84.86</v>
+      </c>
+      <c r="O33" t="n">
+        <v>4</v>
+      </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
@@ -1957,6 +2361,18 @@
       <c r="K34" t="n">
         <v>50</v>
       </c>
+      <c r="L34" t="n">
+        <v>11.38</v>
+      </c>
+      <c r="M34" t="n">
+        <v>14</v>
+      </c>
+      <c r="N34" t="n">
+        <v>81.29000000000001</v>
+      </c>
+      <c r="O34" t="n">
+        <v>7</v>
+      </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
@@ -2002,6 +2418,18 @@
       <c r="K35" t="n">
         <v>50</v>
       </c>
+      <c r="L35" t="n">
+        <v>11.9</v>
+      </c>
+      <c r="M35" t="n">
+        <v>14</v>
+      </c>
+      <c r="N35" t="n">
+        <v>85.01000000000001</v>
+      </c>
+      <c r="O35" t="n">
+        <v>5</v>
+      </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
@@ -2047,6 +2475,18 @@
       <c r="K36" t="n">
         <v>50</v>
       </c>
+      <c r="L36" t="n">
+        <v>11.96</v>
+      </c>
+      <c r="M36" t="n">
+        <v>14</v>
+      </c>
+      <c r="N36" t="n">
+        <v>85.44</v>
+      </c>
+      <c r="O36" t="n">
+        <v>5</v>
+      </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
@@ -2092,6 +2532,18 @@
       <c r="K37" t="n">
         <v>50</v>
       </c>
+      <c r="L37" t="n">
+        <v>11.76</v>
+      </c>
+      <c r="M37" t="n">
+        <v>14</v>
+      </c>
+      <c r="N37" t="n">
+        <v>84.01000000000001</v>
+      </c>
+      <c r="O37" t="n">
+        <v>6</v>
+      </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
@@ -2137,6 +2589,18 @@
       <c r="K38" t="n">
         <v>50</v>
       </c>
+      <c r="L38" t="n">
+        <v>11.74</v>
+      </c>
+      <c r="M38" t="n">
+        <v>14</v>
+      </c>
+      <c r="N38" t="n">
+        <v>83.86</v>
+      </c>
+      <c r="O38" t="n">
+        <v>4</v>
+      </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
@@ -2182,6 +2646,18 @@
       <c r="K39" t="n">
         <v>50</v>
       </c>
+      <c r="L39" t="n">
+        <v>11.92</v>
+      </c>
+      <c r="M39" t="n">
+        <v>14</v>
+      </c>
+      <c r="N39" t="n">
+        <v>85.15000000000001</v>
+      </c>
+      <c r="O39" t="n">
+        <v>4</v>
+      </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
@@ -2227,6 +2703,18 @@
       <c r="K40" t="n">
         <v>50</v>
       </c>
+      <c r="L40" t="n">
+        <v>11.96</v>
+      </c>
+      <c r="M40" t="n">
+        <v>14</v>
+      </c>
+      <c r="N40" t="n">
+        <v>85.44</v>
+      </c>
+      <c r="O40" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
@@ -2272,6 +2760,18 @@
       <c r="K41" t="n">
         <v>50</v>
       </c>
+      <c r="L41" t="n">
+        <v>12.32</v>
+      </c>
+      <c r="M41" t="n">
+        <v>14</v>
+      </c>
+      <c r="N41" t="n">
+        <v>88.01000000000001</v>
+      </c>
+      <c r="O41" t="n">
+        <v>3</v>
+      </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
@@ -2317,6 +2817,18 @@
       <c r="K42" t="n">
         <v>50</v>
       </c>
+      <c r="L42" t="n">
+        <v>11.46</v>
+      </c>
+      <c r="M42" t="n">
+        <v>14</v>
+      </c>
+      <c r="N42" t="n">
+        <v>81.86</v>
+      </c>
+      <c r="O42" t="n">
+        <v>9</v>
+      </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
@@ -2362,6 +2874,18 @@
       <c r="K43" t="n">
         <v>50</v>
       </c>
+      <c r="L43" t="n">
+        <v>11.72</v>
+      </c>
+      <c r="M43" t="n">
+        <v>14</v>
+      </c>
+      <c r="N43" t="n">
+        <v>83.72</v>
+      </c>
+      <c r="O43" t="n">
+        <v>6</v>
+      </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
@@ -2407,6 +2931,18 @@
       <c r="K44" t="n">
         <v>50</v>
       </c>
+      <c r="L44" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="M44" t="n">
+        <v>14</v>
+      </c>
+      <c r="N44" t="n">
+        <v>82.15000000000001</v>
+      </c>
+      <c r="O44" t="n">
+        <v>7</v>
+      </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
@@ -2452,6 +2988,18 @@
       <c r="K45" t="n">
         <v>50</v>
       </c>
+      <c r="L45" t="n">
+        <v>11.56</v>
+      </c>
+      <c r="M45" t="n">
+        <v>14</v>
+      </c>
+      <c r="N45" t="n">
+        <v>82.58</v>
+      </c>
+      <c r="O45" t="n">
+        <v>8</v>
+      </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
@@ -2497,6 +3045,18 @@
       <c r="K46" t="n">
         <v>50</v>
       </c>
+      <c r="L46" t="n">
+        <v>11.62</v>
+      </c>
+      <c r="M46" t="n">
+        <v>14</v>
+      </c>
+      <c r="N46" t="n">
+        <v>83.01000000000001</v>
+      </c>
+      <c r="O46" t="n">
+        <v>4</v>
+      </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
@@ -2542,6 +3102,18 @@
       <c r="K47" t="n">
         <v>50</v>
       </c>
+      <c r="L47" t="n">
+        <v>11.48</v>
+      </c>
+      <c r="M47" t="n">
+        <v>14</v>
+      </c>
+      <c r="N47" t="n">
+        <v>82</v>
+      </c>
+      <c r="O47" t="n">
+        <v>5</v>
+      </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
@@ -2587,6 +3159,18 @@
       <c r="K48" t="n">
         <v>50</v>
       </c>
+      <c r="L48" t="n">
+        <v>11.88</v>
+      </c>
+      <c r="M48" t="n">
+        <v>14</v>
+      </c>
+      <c r="N48" t="n">
+        <v>84.87</v>
+      </c>
+      <c r="O48" t="n">
+        <v>4</v>
+      </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
@@ -2632,6 +3216,18 @@
       <c r="K49" t="n">
         <v>50</v>
       </c>
+      <c r="L49" t="n">
+        <v>11.72</v>
+      </c>
+      <c r="M49" t="n">
+        <v>14</v>
+      </c>
+      <c r="N49" t="n">
+        <v>83.73</v>
+      </c>
+      <c r="O49" t="n">
+        <v>5</v>
+      </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
@@ -2677,6 +3273,18 @@
       <c r="K50" t="n">
         <v>50</v>
       </c>
+      <c r="L50" t="n">
+        <v>11.78</v>
+      </c>
+      <c r="M50" t="n">
+        <v>14</v>
+      </c>
+      <c r="N50" t="n">
+        <v>84.15000000000001</v>
+      </c>
+      <c r="O50" t="n">
+        <v>4</v>
+      </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
@@ -2722,6 +3330,18 @@
       <c r="K51" t="n">
         <v>50</v>
       </c>
+      <c r="L51" t="n">
+        <v>12.04</v>
+      </c>
+      <c r="M51" t="n">
+        <v>14</v>
+      </c>
+      <c r="N51" t="n">
+        <v>86.01000000000001</v>
+      </c>
+      <c r="O51" t="n">
+        <v>3</v>
+      </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
@@ -2767,6 +3387,18 @@
       <c r="K52" t="n">
         <v>50</v>
       </c>
+      <c r="L52" t="n">
+        <v>12.14</v>
+      </c>
+      <c r="M52" t="n">
+        <v>14</v>
+      </c>
+      <c r="N52" t="n">
+        <v>86.72</v>
+      </c>
+      <c r="O52" t="n">
+        <v>2</v>
+      </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
@@ -2812,6 +3444,18 @@
       <c r="K53" t="n">
         <v>50</v>
       </c>
+      <c r="L53" t="n">
+        <v>11.66</v>
+      </c>
+      <c r="M53" t="n">
+        <v>14</v>
+      </c>
+      <c r="N53" t="n">
+        <v>83.29000000000001</v>
+      </c>
+      <c r="O53" t="n">
+        <v>7</v>
+      </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
@@ -2857,6 +3501,18 @@
       <c r="K54" t="n">
         <v>50</v>
       </c>
+      <c r="L54" t="n">
+        <v>11.16</v>
+      </c>
+      <c r="M54" t="n">
+        <v>14</v>
+      </c>
+      <c r="N54" t="n">
+        <v>79.70999999999999</v>
+      </c>
+      <c r="O54" t="n">
+        <v>10</v>
+      </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
@@ -2902,6 +3558,18 @@
       <c r="K55" t="n">
         <v>50</v>
       </c>
+      <c r="L55" t="n">
+        <v>11.72</v>
+      </c>
+      <c r="M55" t="n">
+        <v>14</v>
+      </c>
+      <c r="N55" t="n">
+        <v>83.73</v>
+      </c>
+      <c r="O55" t="n">
+        <v>5</v>
+      </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
@@ -2947,6 +3615,18 @@
       <c r="K56" t="n">
         <v>50</v>
       </c>
+      <c r="L56" t="n">
+        <v>11.62</v>
+      </c>
+      <c r="M56" t="n">
+        <v>14</v>
+      </c>
+      <c r="N56" t="n">
+        <v>83.01000000000001</v>
+      </c>
+      <c r="O56" t="n">
+        <v>5</v>
+      </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
@@ -2992,6 +3672,18 @@
       <c r="K57" t="n">
         <v>50</v>
       </c>
+      <c r="L57" t="n">
+        <v>11.52</v>
+      </c>
+      <c r="M57" t="n">
+        <v>14</v>
+      </c>
+      <c r="N57" t="n">
+        <v>82.29000000000001</v>
+      </c>
+      <c r="O57" t="n">
+        <v>6</v>
+      </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
@@ -3037,6 +3729,18 @@
       <c r="K58" t="n">
         <v>50</v>
       </c>
+      <c r="L58" t="n">
+        <v>10.8</v>
+      </c>
+      <c r="M58" t="n">
+        <v>14</v>
+      </c>
+      <c r="N58" t="n">
+        <v>77.15000000000001</v>
+      </c>
+      <c r="O58" t="n">
+        <v>15</v>
+      </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
@@ -3082,6 +3786,18 @@
       <c r="K59" t="n">
         <v>50</v>
       </c>
+      <c r="L59" t="n">
+        <v>11.02</v>
+      </c>
+      <c r="M59" t="n">
+        <v>14</v>
+      </c>
+      <c r="N59" t="n">
+        <v>78.72</v>
+      </c>
+      <c r="O59" t="n">
+        <v>9</v>
+      </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
@@ -3127,6 +3843,18 @@
       <c r="K60" t="n">
         <v>50</v>
       </c>
+      <c r="L60" t="n">
+        <v>10.72</v>
+      </c>
+      <c r="M60" t="n">
+        <v>14</v>
+      </c>
+      <c r="N60" t="n">
+        <v>76.58</v>
+      </c>
+      <c r="O60" t="n">
+        <v>12</v>
+      </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
@@ -3172,6 +3900,18 @@
       <c r="K61" t="n">
         <v>50</v>
       </c>
+      <c r="L61" t="n">
+        <v>10.78</v>
+      </c>
+      <c r="M61" t="n">
+        <v>14</v>
+      </c>
+      <c r="N61" t="n">
+        <v>77</v>
+      </c>
+      <c r="O61" t="n">
+        <v>12</v>
+      </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
@@ -3217,6 +3957,18 @@
       <c r="K62" t="n">
         <v>50</v>
       </c>
+      <c r="L62" t="n">
+        <v>11.28</v>
+      </c>
+      <c r="M62" t="n">
+        <v>14</v>
+      </c>
+      <c r="N62" t="n">
+        <v>80.58</v>
+      </c>
+      <c r="O62" t="n">
+        <v>11</v>
+      </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
@@ -3262,6 +4014,18 @@
       <c r="K63" t="n">
         <v>50</v>
       </c>
+      <c r="L63" t="n">
+        <v>11.36</v>
+      </c>
+      <c r="M63" t="n">
+        <v>14</v>
+      </c>
+      <c r="N63" t="n">
+        <v>81.15000000000001</v>
+      </c>
+      <c r="O63" t="n">
+        <v>13</v>
+      </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
@@ -3307,6 +4071,18 @@
       <c r="K64" t="n">
         <v>50</v>
       </c>
+      <c r="L64" t="n">
+        <v>11.02</v>
+      </c>
+      <c r="M64" t="n">
+        <v>14</v>
+      </c>
+      <c r="N64" t="n">
+        <v>78.72</v>
+      </c>
+      <c r="O64" t="n">
+        <v>13</v>
+      </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
@@ -3352,6 +4128,18 @@
       <c r="K65" t="n">
         <v>50</v>
       </c>
+      <c r="L65" t="n">
+        <v>11</v>
+      </c>
+      <c r="M65" t="n">
+        <v>14</v>
+      </c>
+      <c r="N65" t="n">
+        <v>78.58</v>
+      </c>
+      <c r="O65" t="n">
+        <v>10</v>
+      </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
@@ -3397,6 +4185,18 @@
       <c r="K66" t="n">
         <v>50</v>
       </c>
+      <c r="L66" t="n">
+        <v>11.24</v>
+      </c>
+      <c r="M66" t="n">
+        <v>14</v>
+      </c>
+      <c r="N66" t="n">
+        <v>80.29000000000001</v>
+      </c>
+      <c r="O66" t="n">
+        <v>11</v>
+      </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
@@ -3442,6 +4242,18 @@
       <c r="K67" t="n">
         <v>50</v>
       </c>
+      <c r="L67" t="n">
+        <v>11.12</v>
+      </c>
+      <c r="M67" t="n">
+        <v>14</v>
+      </c>
+      <c r="N67" t="n">
+        <v>79.43000000000001</v>
+      </c>
+      <c r="O67" t="n">
+        <v>9</v>
+      </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
@@ -3487,6 +4299,18 @@
       <c r="K68" t="n">
         <v>50</v>
       </c>
+      <c r="L68" t="n">
+        <v>11.26</v>
+      </c>
+      <c r="M68" t="n">
+        <v>14</v>
+      </c>
+      <c r="N68" t="n">
+        <v>80.43000000000001</v>
+      </c>
+      <c r="O68" t="n">
+        <v>7</v>
+      </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
@@ -3532,6 +4356,18 @@
       <c r="K69" t="n">
         <v>50</v>
       </c>
+      <c r="L69" t="n">
+        <v>11.14</v>
+      </c>
+      <c r="M69" t="n">
+        <v>14</v>
+      </c>
+      <c r="N69" t="n">
+        <v>79.58</v>
+      </c>
+      <c r="O69" t="n">
+        <v>9</v>
+      </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
@@ -3577,6 +4413,18 @@
       <c r="K70" t="n">
         <v>50</v>
       </c>
+      <c r="L70" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="M70" t="n">
+        <v>14</v>
+      </c>
+      <c r="N70" t="n">
+        <v>82.15000000000001</v>
+      </c>
+      <c r="O70" t="n">
+        <v>7</v>
+      </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
@@ -3622,6 +4470,18 @@
       <c r="K71" t="n">
         <v>50</v>
       </c>
+      <c r="L71" t="n">
+        <v>11.42</v>
+      </c>
+      <c r="M71" t="n">
+        <v>14</v>
+      </c>
+      <c r="N71" t="n">
+        <v>81.56999999999999</v>
+      </c>
+      <c r="O71" t="n">
+        <v>7</v>
+      </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
@@ -3667,6 +4527,18 @@
       <c r="K72" t="n">
         <v>50</v>
       </c>
+      <c r="L72" t="n">
+        <v>11.78</v>
+      </c>
+      <c r="M72" t="n">
+        <v>14</v>
+      </c>
+      <c r="N72" t="n">
+        <v>84.15000000000001</v>
+      </c>
+      <c r="O72" t="n">
+        <v>5</v>
+      </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
@@ -3711,6 +4583,18 @@
       </c>
       <c r="K73" t="n">
         <v>50</v>
+      </c>
+      <c r="L73" t="n">
+        <v>11.16</v>
+      </c>
+      <c r="M73" t="n">
+        <v>14</v>
+      </c>
+      <c r="N73" t="n">
+        <v>79.70999999999999</v>
+      </c>
+      <c r="O73" t="n">
+        <v>9</v>
       </c>
     </row>
   </sheetData>
